--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1237</v>
+        <v>5.1259</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-1.30027</v>
+        <v>-1.257898</v>
       </c>
     </row>
     <row r="124">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9496</v>
+        <v>5.9594</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-0.998645</v>
+        <v>-0.835574</v>
       </c>
     </row>
     <row r="246">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>536.75</v>
+        <v>512</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>4.223301</v>
+        <v>-0.582524</v>
       </c>
     </row>
     <row r="429">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1309.75</v>
+        <v>1293.75</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>2.705352</v>
+        <v>1.450696</v>
       </c>
     </row>
     <row r="795">

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9594</v>
+        <v>5.9606</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-0.835574</v>
+        <v>-0.8156099999999999</v>
       </c>
     </row>
     <row r="246">

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>181.940002</v>
+        <v>186.029999</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>4.096581</v>
+        <v>6.436663</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1259</v>
+        <v>5.0806</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-1.257898</v>
+        <v>-2.130529</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>53414.25</v>
+        <v>52819.558594</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>0.429346</v>
+        <v>-0.688791</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9606</v>
+        <v>5.9044</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-0.8156099999999999</v>
+        <v>-1.750779</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>185147</v>
+        <v>188913.453125</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>4.355791</v>
+        <v>6.478705</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>447.350006</v>
+        <v>439.269989</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-0.445087</v>
+        <v>-2.243244</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>512</v>
+        <v>535.5</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-0.582524</v>
+        <v>3.980583</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26506.990234</v>
+        <v>26390.132812</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>0.5160979999999999</v>
+        <v>0.07296800000000001</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4476.600098</v>
+        <v>4442</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>1.026833</v>
+        <v>0.245986</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>96.279999</v>
+        <v>98.08000199999999</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>6.398498</v>
+        <v>8.387672</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>91.480003</v>
+        <v>93.269997</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>6.669777</v>
+        <v>8.75699</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>110.989998</v>
+        <v>112.760002</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>4.57929</v>
+        <v>6.24706</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1293.75</v>
+        <v>1307.25</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>1.450696</v>
+        <v>2.509312</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7718.600098</v>
+        <v>7684.339844</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>0.422318</v>
+        <v>-0.023423</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>186.029999</v>
+        <v>184.070007</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>6.436663</v>
+        <v>5.315258</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.0806</v>
+        <v>5.0937</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-2.130529</v>
+        <v>-1.878176</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52819.558594</v>
+        <v>52381.640625</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-0.688791</v>
+        <v>-1.512164</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9044</v>
+        <v>5.9353</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.750779</v>
+        <v>-1.236603</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>188913.453125</v>
+        <v>187042.90625</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>6.478705</v>
+        <v>5.424394</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>439.269989</v>
+        <v>440.329987</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-2.243244</v>
+        <v>-2.007348</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>535.5</v>
+        <v>527.25</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>3.980583</v>
+        <v>2.378641</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26390.132812</v>
+        <v>26360.449219</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>0.07296800000000001</v>
+        <v>-0.039594</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4442</v>
+        <v>4456.600098</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>0.245986</v>
+        <v>0.575478</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>98.08000199999999</v>
+        <v>100.669998</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>8.387672</v>
+        <v>11.249862</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>93.269997</v>
+        <v>95.75</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>8.75699</v>
+        <v>11.648785</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>112.760002</v>
+        <v>111.110001</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>6.24706</v>
+        <v>4.692362</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1307.25</v>
+        <v>1308.75</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>2.509312</v>
+        <v>2.626936</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7684.339844</v>
+        <v>7653.459961</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-0.023423</v>
+        <v>-0.425183</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>184.070007</v>
+        <v>182.330002</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>5.315258</v>
+        <v>4.319718</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.0937</v>
+        <v>5.1422</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-1.878176</v>
+        <v>-0.943901</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52381.640625</v>
+        <v>52079.46875</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-1.512164</v>
+        <v>-2.080306</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9353</v>
+        <v>5.9703</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.236603</v>
+        <v>-0.654197</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>187042.90625</v>
+        <v>185144.859375</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>5.424394</v>
+        <v>4.354584</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>440.329987</v>
+        <v>440.929993</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-2.007348</v>
+        <v>-1.873821</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>527.25</v>
+        <v>528</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>2.378641</v>
+        <v>2.524272</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26360.449219</v>
+        <v>26037.785156</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-0.039594</v>
+        <v>-1.263156</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4456.600098</v>
+        <v>4409.5</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>0.575478</v>
+        <v>-0.487466</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>100.669998</v>
+        <v>104.540001</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>11.249862</v>
+        <v>15.526581</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>95.75</v>
+        <v>99.300003</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>11.648785</v>
+        <v>15.788247</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>111.110001</v>
+        <v>109.870003</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>4.692362</v>
+        <v>3.523985</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1308.75</v>
+        <v>1316</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>2.626936</v>
+        <v>3.195452</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7653.459961</v>
+        <v>7583.859863</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-0.425183</v>
+        <v>-1.33071</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>182.330002</v>
+        <v>184.119995</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>4.319718</v>
+        <v>5.343859</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1422</v>
+        <v>5.083</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-0.943901</v>
+        <v>-2.084289</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52079.46875</v>
+        <v>52662.679688</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-2.080306</v>
+        <v>-0.983755</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9703</v>
+        <v>5.9061</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-0.654197</v>
+        <v>-1.722492</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>185144.859375</v>
+        <v>187021.609375</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>4.354584</v>
+        <v>5.412391</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>440.929993</v>
+        <v>440.160004</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.873821</v>
+        <v>-2.045177</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>528</v>
+        <v>525.5</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>2.524272</v>
+        <v>2.038835</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26037.785156</v>
+        <v>26405.673828</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-1.263156</v>
+        <v>0.1319</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4409.5</v>
+        <v>4432.399902</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-0.487466</v>
+        <v>0.029334</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>104.540001</v>
+        <v>104.110001</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>15.526581</v>
+        <v>15.05139</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>99.300003</v>
+        <v>98.75</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>15.788247</v>
+        <v>15.146919</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>109.870003</v>
+        <v>111.400002</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>3.523985</v>
+        <v>4.965612</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1316</v>
+        <v>1311.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>3.195452</v>
+        <v>2.84258</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7583.859863</v>
+        <v>7675.77002</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-1.33071</v>
+        <v>-0.13492</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>184.119995</v>
+        <v>184.139999</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>5.343859</v>
+        <v>5.355304</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.083</v>
+        <v>5.0901</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-2.084289</v>
+        <v>-1.947526</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52662.679688</v>
+        <v>52650.328125</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-0.983755</v>
+        <v>-1.006978</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9061</v>
+        <v>5.9107</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.722492</v>
+        <v>-1.645947</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>187021.609375</v>
+        <v>187039.734375</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>5.412391</v>
+        <v>5.422607</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>440.160004</v>
+        <v>440.209991</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-2.045177</v>
+        <v>-2.034052</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>525.5</v>
+        <v>525.25</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>2.038835</v>
+        <v>1.990291</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26405.673828</v>
+        <v>26356.910156</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>0.1319</v>
+        <v>-0.053015</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4432.399902</v>
+        <v>4430.5</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>0.029334</v>
+        <v>-0.013543</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>104.110001</v>
+        <v>104.43</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>15.05139</v>
+        <v>15.40502</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>98.75</v>
+        <v>99.050003</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>15.146919</v>
+        <v>15.496736</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>111.400002</v>
+        <v>111.370003</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>4.965612</v>
+        <v>4.937346</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1311.5</v>
+        <v>1310.75</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>2.84258</v>
+        <v>2.783768</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7675.77002</v>
+        <v>7664.779785</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-0.13492</v>
+        <v>-0.277907</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>184.139999</v>
+        <v>185.210007</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>5.355304</v>
+        <v>5.967507</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.0901</v>
+        <v>5.1262</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-1.947526</v>
+        <v>-1.252111</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52650.328125</v>
+        <v>52573.289062</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-1.006978</v>
+        <v>-1.151827</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9107</v>
+        <v>5.9463</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.645947</v>
+        <v>-1.05356</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>187039.734375</v>
+        <v>187207</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>5.422607</v>
+        <v>5.516884</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>440.209991</v>
+        <v>437.649994</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-2.034052</v>
+        <v>-2.603764</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>525.25</v>
+        <v>510.25</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>1.990291</v>
+        <v>-0.92233</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26356.910156</v>
+        <v>26333.039062</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-0.053015</v>
+        <v>-0.143535</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4430.5</v>
+        <v>4366.200195</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-0.013543</v>
+        <v>-1.464645</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>104.43</v>
+        <v>104.610001</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>15.40502</v>
+        <v>15.603938</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>99.050003</v>
+        <v>100.050003</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>15.496736</v>
+        <v>16.662781</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>111.370003</v>
+        <v>112.300003</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>4.937346</v>
+        <v>5.81363</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1310.75</v>
+        <v>1280.25</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>2.783768</v>
+        <v>0.39208</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7664.779785</v>
+        <v>7656.97998</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-0.277907</v>
+        <v>-0.379386</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>185.210007</v>
+        <v>183.850006</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>5.967507</v>
+        <v>5.189385</v>
       </c>
     </row>
     <row r="63">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>437.649994</v>
+        <v>443.149994</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-2.603764</v>
+        <v>-1.379773</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>510.25</v>
+        <v>532</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-0.92233</v>
+        <v>3.300971</v>
       </c>
     </row>
     <row r="429">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4366.200195</v>
+        <v>4408.899902</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-1.464645</v>
+        <v>-0.501009</v>
       </c>
     </row>
     <row r="551">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>112.300003</v>
+        <v>110.830002</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>5.81363</v>
+        <v>4.428535</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1280.25</v>
+        <v>1299</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>0.39208</v>
+        <v>1.86238</v>
       </c>
     </row>
     <row r="795">

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>183.850006</v>
+        <v>182.369995</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>5.189385</v>
+        <v>4.3426</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1262</v>
+        <v>5.1539</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-1.252111</v>
+        <v>-0.718517</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52573.289062</v>
+        <v>52482.101562</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-1.151827</v>
+        <v>-1.323277</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9463</v>
+        <v>5.9512</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.05356</v>
+        <v>-0.972025</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>187207</v>
+        <v>185371.140625</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>5.516884</v>
+        <v>4.482125</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>443.149994</v>
+        <v>443.630005</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.379773</v>
+        <v>-1.27295</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>532</v>
+        <v>530.5</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>3.300971</v>
+        <v>3.009709</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26333.039062</v>
+        <v>26209.451172</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-0.143535</v>
+        <v>-0.612188</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4408.899902</v>
+        <v>4331.600098</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-0.501009</v>
+        <v>-2.245492</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>104.610001</v>
+        <v>107.419998</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>15.603938</v>
+        <v>18.70925</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>100.050003</v>
+        <v>102.970001</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>16.662781</v>
+        <v>20.067629</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>110.830002</v>
+        <v>109.68</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>4.428535</v>
+        <v>3.344957</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1299</v>
+        <v>1306.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>1.86238</v>
+        <v>2.4505</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7656.97998</v>
+        <v>7626.77002</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-0.379386</v>
+        <v>-0.772431</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>182.369995</v>
+        <v>183.039993</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>4.3426</v>
+        <v>4.725938</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1539</v>
+        <v>5.1456</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-0.718517</v>
+        <v>-0.878408</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52482.101562</v>
+        <v>51923.578125</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-1.323277</v>
+        <v>-2.373412</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9512</v>
+        <v>5.9456</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-0.972025</v>
+        <v>-1.065208</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>185371.140625</v>
+        <v>185959.625</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>4.482125</v>
+        <v>4.813816</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>443.630005</v>
+        <v>440.839996</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.27295</v>
+        <v>-1.893849</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>530.5</v>
+        <v>531.25</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>3.009709</v>
+        <v>3.15534</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26209.451172</v>
+        <v>26026.601562</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-0.612188</v>
+        <v>-1.305565</v>
       </c>
     </row>
     <row r="490">
@@ -32719,7 +32719,7 @@
         </is>
       </c>
       <c r="H490" t="n">
-        <v>1755.300049</v>
+        <v>1757</v>
       </c>
       <c r="I490" t="inlineStr">
         <is>
@@ -32783,7 +32783,7 @@
         </is>
       </c>
       <c r="H491" t="n">
-        <v>1783</v>
+        <v>1783.900024</v>
       </c>
       <c r="I491" t="inlineStr">
         <is>
@@ -32811,7 +32811,7 @@
         </is>
       </c>
       <c r="N491" t="n">
-        <v>1.578075</v>
+        <v>1.53102</v>
       </c>
     </row>
     <row r="492">
@@ -32877,7 +32877,7 @@
         </is>
       </c>
       <c r="N492" t="n">
-        <v>-0.527203</v>
+        <v>-0.577389</v>
       </c>
     </row>
     <row r="493">
@@ -32915,7 +32915,7 @@
         </is>
       </c>
       <c r="H493" t="n">
-        <v>1827.5</v>
+        <v>1828.599976</v>
       </c>
       <c r="I493" t="inlineStr">
         <is>
@@ -32943,7 +32943,7 @@
         </is>
       </c>
       <c r="N493" t="n">
-        <v>3.039018</v>
+        <v>3.101037</v>
       </c>
     </row>
     <row r="494">
@@ -33009,7 +33009,7 @@
         </is>
       </c>
       <c r="N494" t="n">
-        <v>-1.778386</v>
+        <v>-1.83747</v>
       </c>
     </row>
     <row r="495">
@@ -33047,7 +33047,7 @@
         </is>
       </c>
       <c r="H495" t="n">
-        <v>1899.400024</v>
+        <v>1900.699951</v>
       </c>
       <c r="I495" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         </is>
       </c>
       <c r="N495" t="n">
-        <v>5.816157</v>
+        <v>5.888577</v>
       </c>
     </row>
     <row r="496">
@@ -33141,7 +33141,7 @@
         </is>
       </c>
       <c r="N496" t="n">
-        <v>2.621877</v>
+        <v>2.551692</v>
       </c>
     </row>
     <row r="497">
@@ -33179,7 +33179,7 @@
         </is>
       </c>
       <c r="H497" t="n">
-        <v>1909.300049</v>
+        <v>1911.699951</v>
       </c>
       <c r="I497" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         </is>
       </c>
       <c r="N497" t="n">
-        <v>-2.046989</v>
+        <v>-1.923866</v>
       </c>
     </row>
     <row r="498">
@@ -33273,7 +33273,7 @@
         </is>
       </c>
       <c r="N498" t="n">
-        <v>-3.488194</v>
+        <v>-3.609353</v>
       </c>
     </row>
     <row r="499">
@@ -33311,7 +33311,7 @@
         </is>
       </c>
       <c r="H499" t="n">
-        <v>1804.099976</v>
+        <v>1807.300049</v>
       </c>
       <c r="I499" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         </is>
       </c>
       <c r="N499" t="n">
-        <v>-2.094751</v>
+        <v>-1.921089</v>
       </c>
     </row>
     <row r="500">
@@ -33405,7 +33405,7 @@
         </is>
       </c>
       <c r="N500" t="n">
-        <v>-2.283684</v>
+        <v>-2.456705</v>
       </c>
     </row>
     <row r="501">
@@ -33443,7 +33443,7 @@
         </is>
       </c>
       <c r="H501" t="n">
-        <v>1712.800049</v>
+        <v>1726.199951</v>
       </c>
       <c r="I501" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         </is>
       </c>
       <c r="N501" t="n">
-        <v>-2.841907</v>
+        <v>-2.081801</v>
       </c>
     </row>
     <row r="502">
@@ -33509,7 +33509,7 @@
         </is>
       </c>
       <c r="H502" t="n">
-        <v>1662.400024</v>
+        <v>1672</v>
       </c>
       <c r="I502" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         </is>
       </c>
       <c r="N502" t="n">
-        <v>-2.942552</v>
+        <v>-3.139842</v>
       </c>
     </row>
     <row r="503">
@@ -33575,7 +33575,7 @@
         </is>
       </c>
       <c r="H503" t="n">
-        <v>1635.900024</v>
+        <v>1640.699951</v>
       </c>
       <c r="I503" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         </is>
       </c>
       <c r="N503" t="n">
-        <v>-1.594081</v>
+        <v>-1.872012</v>
       </c>
     </row>
     <row r="504">
@@ -33669,7 +33669,7 @@
         </is>
       </c>
       <c r="N504" t="n">
-        <v>6.730239</v>
+        <v>6.417995</v>
       </c>
     </row>
     <row r="505">
@@ -33707,7 +33707,7 @@
         </is>
       </c>
       <c r="H505" t="n">
-        <v>1819.699951</v>
+        <v>1826.199951</v>
       </c>
       <c r="I505" t="inlineStr">
         <is>
@@ -33735,7 +33735,7 @@
         </is>
       </c>
       <c r="N505" t="n">
-        <v>4.221074</v>
+        <v>4.593353</v>
       </c>
     </row>
     <row r="506">
@@ -33801,7 +33801,7 @@
         </is>
       </c>
       <c r="N506" t="n">
-        <v>6.033964</v>
+        <v>5.656557</v>
       </c>
     </row>
     <row r="507">
@@ -33839,7 +33839,7 @@
         </is>
       </c>
       <c r="H507" t="n">
-        <v>1828.900024</v>
+        <v>1836.699951</v>
       </c>
       <c r="I507" t="inlineStr">
         <is>
@@ -33867,7 +33867,7 @@
         </is>
       </c>
       <c r="N507" t="n">
-        <v>-5.213785</v>
+        <v>-4.809539</v>
       </c>
     </row>
     <row r="508">
@@ -33933,7 +33933,7 @@
         </is>
       </c>
       <c r="N508" t="n">
-        <v>7.660341</v>
+        <v>7.203139</v>
       </c>
     </row>
     <row r="509">
@@ -33971,7 +33971,7 @@
         </is>
       </c>
       <c r="H509" t="n">
-        <v>1990.099976</v>
+        <v>1999.099976</v>
       </c>
       <c r="I509" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
         </is>
       </c>
       <c r="N509" t="n">
-        <v>1.071609</v>
+        <v>1.528694</v>
       </c>
     </row>
     <row r="510">
@@ -34065,7 +34065,7 @@
         </is>
       </c>
       <c r="N510" t="n">
-        <v>-1.316514</v>
+        <v>-1.76079</v>
       </c>
     </row>
     <row r="511">
@@ -34103,7 +34103,7 @@
         </is>
       </c>
       <c r="H511" t="n">
-        <v>1921.099976</v>
+        <v>1929.400024</v>
       </c>
       <c r="I511" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         </is>
       </c>
       <c r="N511" t="n">
-        <v>-2.179339</v>
+        <v>-1.756709</v>
       </c>
     </row>
     <row r="512">
@@ -34197,7 +34197,7 @@
         </is>
       </c>
       <c r="N512" t="n">
-        <v>2.571445</v>
+        <v>2.130195</v>
       </c>
     </row>
     <row r="513">
@@ -34235,7 +34235,7 @@
         </is>
       </c>
       <c r="H513" t="n">
-        <v>1938.199951</v>
+        <v>1965.900024</v>
       </c>
       <c r="I513" t="inlineStr">
         <is>
@@ -34263,7 +34263,7 @@
         </is>
       </c>
       <c r="N513" t="n">
-        <v>-1.63918</v>
+        <v>-0.233442</v>
       </c>
     </row>
     <row r="514">
@@ -34301,7 +34301,7 @@
         </is>
       </c>
       <c r="H514" t="n">
-        <v>1848.099976</v>
+        <v>1866.099976</v>
       </c>
       <c r="I514" t="inlineStr">
         <is>
@@ -34329,7 +34329,7 @@
         </is>
       </c>
       <c r="N514" t="n">
-        <v>-4.648642</v>
+        <v>-5.076558</v>
       </c>
     </row>
     <row r="515">
@@ -34367,7 +34367,7 @@
         </is>
       </c>
       <c r="H515" t="n">
-        <v>1985.199951</v>
+        <v>1994.300049</v>
       </c>
       <c r="I515" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         </is>
       </c>
       <c r="N515" t="n">
-        <v>7.418429</v>
+        <v>6.869947</v>
       </c>
     </row>
     <row r="516">
@@ -34461,7 +34461,7 @@
         </is>
       </c>
       <c r="N516" t="n">
-        <v>2.66472</v>
+        <v>2.196256</v>
       </c>
     </row>
     <row r="517">
@@ -34499,7 +34499,7 @@
         </is>
       </c>
       <c r="H517" t="n">
-        <v>2062.399902</v>
+        <v>2071.800049</v>
       </c>
       <c r="I517" t="inlineStr">
         <is>
@@ -34527,7 +34527,7 @@
         </is>
       </c>
       <c r="N517" t="n">
-        <v>1.192283</v>
+        <v>1.653504</v>
       </c>
     </row>
     <row r="518">
@@ -34593,7 +34593,7 @@
         </is>
       </c>
       <c r="N518" t="n">
-        <v>-0.678821</v>
+        <v>-1.12946</v>
       </c>
     </row>
     <row r="519">
@@ -34631,7 +34631,7 @@
         </is>
       </c>
       <c r="H519" t="n">
-        <v>2045.699951</v>
+        <v>2054.699951</v>
       </c>
       <c r="I519" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         </is>
       </c>
       <c r="N519" t="n">
-        <v>-0.131808</v>
+        <v>0.30756</v>
       </c>
     </row>
     <row r="520">
@@ -34725,7 +34725,7 @@
         </is>
       </c>
       <c r="N520" t="n">
-        <v>8.393212999999999</v>
+        <v>7.918429</v>
       </c>
     </row>
     <row r="521">
@@ -34763,7 +34763,7 @@
         </is>
       </c>
       <c r="H521" t="n">
-        <v>2291.399902</v>
+        <v>2302.899902</v>
       </c>
       <c r="I521" t="inlineStr">
         <is>
@@ -34791,7 +34791,7 @@
         </is>
       </c>
       <c r="N521" t="n">
-        <v>3.337242</v>
+        <v>3.855867</v>
       </c>
     </row>
     <row r="522">
@@ -34857,7 +34857,7 @@
         </is>
       </c>
       <c r="N522" t="n">
-        <v>1.374705</v>
+        <v>0.86847</v>
       </c>
     </row>
     <row r="523">
@@ -34895,7 +34895,7 @@
         </is>
       </c>
       <c r="H523" t="n">
-        <v>2327.699951</v>
+        <v>2339.600098</v>
       </c>
       <c r="I523" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         </is>
       </c>
       <c r="N523" t="n">
-        <v>0.20664</v>
+        <v>0.718937</v>
       </c>
     </row>
     <row r="524">
@@ -34989,7 +34989,7 @@
         </is>
       </c>
       <c r="N524" t="n">
-        <v>4.244535</v>
+        <v>3.714306</v>
       </c>
     </row>
     <row r="525">
@@ -35027,7 +35027,7 @@
         </is>
       </c>
       <c r="H525" t="n">
-        <v>2493.800049</v>
+        <v>2527.600098</v>
       </c>
       <c r="I525" t="inlineStr">
         <is>
@@ -35055,7 +35055,7 @@
         </is>
       </c>
       <c r="N525" t="n">
-        <v>2.773544</v>
+        <v>4.166499</v>
       </c>
     </row>
     <row r="526">
@@ -35093,7 +35093,7 @@
         </is>
       </c>
       <c r="H526" t="n">
-        <v>2636.100098</v>
+        <v>2659.399902</v>
       </c>
       <c r="I526" t="inlineStr">
         <is>
@@ -35121,7 +35121,7 @@
         </is>
       </c>
       <c r="N526" t="n">
-        <v>5.706153</v>
+        <v>5.214425</v>
       </c>
     </row>
     <row r="527">
@@ -35159,7 +35159,7 @@
         </is>
       </c>
       <c r="H527" t="n">
-        <v>2738.300049</v>
+        <v>2749.300049</v>
       </c>
       <c r="I527" t="inlineStr">
         <is>
@@ -35187,7 +35187,7 @@
         </is>
       </c>
       <c r="N527" t="n">
-        <v>3.876937</v>
+        <v>3.380467</v>
       </c>
     </row>
     <row r="528">
@@ -35253,7 +35253,7 @@
         </is>
       </c>
       <c r="N528" t="n">
-        <v>-2.968997</v>
+        <v>-3.35722</v>
       </c>
     </row>
     <row r="529">
@@ -35291,7 +35291,7 @@
         </is>
       </c>
       <c r="H529" t="n">
-        <v>2629.199951</v>
+        <v>2641</v>
       </c>
       <c r="I529" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         </is>
       </c>
       <c r="N529" t="n">
-        <v>-1.046295</v>
+        <v>-0.602183</v>
       </c>
     </row>
     <row r="530">
@@ -35385,7 +35385,7 @@
         </is>
       </c>
       <c r="N530" t="n">
-        <v>6.971704</v>
+        <v>6.493752</v>
       </c>
     </row>
     <row r="531">
@@ -35423,7 +35423,7 @@
         </is>
       </c>
       <c r="H531" t="n">
-        <v>2836.800049</v>
+        <v>2848.5</v>
       </c>
       <c r="I531" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         </is>
       </c>
       <c r="N531" t="n">
-        <v>0.864002</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="532">
@@ -35517,7 +35517,7 @@
         </is>
       </c>
       <c r="N532" t="n">
-        <v>10.081782</v>
+        <v>9.629631</v>
       </c>
     </row>
     <row r="533">
@@ -35555,7 +35555,7 @@
         </is>
       </c>
       <c r="H533" t="n">
-        <v>3305</v>
+        <v>3319.100098</v>
       </c>
       <c r="I533" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         </is>
       </c>
       <c r="N533" t="n">
-        <v>5.834506</v>
+        <v>6.286027</v>
       </c>
     </row>
     <row r="534">
@@ -35649,7 +35649,7 @@
         </is>
       </c>
       <c r="N534" t="n">
-        <v>-0.487144</v>
+        <v>-0.909891</v>
       </c>
     </row>
     <row r="535">
@@ -35687,7 +35687,7 @@
         </is>
       </c>
       <c r="H535" t="n">
-        <v>3294.399902</v>
+        <v>3307.699951</v>
       </c>
       <c r="I535" t="inlineStr">
         <is>
@@ -35715,7 +35715,7 @@
         </is>
       </c>
       <c r="N535" t="n">
-        <v>0.167229</v>
+        <v>0.571621</v>
       </c>
     </row>
     <row r="536">
@@ -35781,7 +35781,7 @@
         </is>
       </c>
       <c r="N536" t="n">
-        <v>-0.036424</v>
+        <v>-0.438371</v>
       </c>
     </row>
     <row r="537">
@@ -35819,7 +35819,7 @@
         </is>
       </c>
       <c r="H537" t="n">
-        <v>3473.699951</v>
+        <v>3516.100098</v>
       </c>
       <c r="I537" t="inlineStr">
         <is>
@@ -35847,7 +35847,7 @@
         </is>
       </c>
       <c r="N537" t="n">
-        <v>5.480991</v>
+        <v>6.768497</v>
       </c>
     </row>
     <row r="538">
@@ -35885,7 +35885,7 @@
         </is>
       </c>
       <c r="H538" t="n">
-        <v>3840.800049</v>
+        <v>3873.199951</v>
       </c>
       <c r="I538" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         </is>
       </c>
       <c r="N538" t="n">
-        <v>10.567985</v>
+        <v>10.156134</v>
       </c>
     </row>
     <row r="539">
@@ -35951,7 +35951,7 @@
         </is>
       </c>
       <c r="H539" t="n">
-        <v>3982.199951</v>
+        <v>3996.5</v>
       </c>
       <c r="I539" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         </is>
       </c>
       <c r="N539" t="n">
-        <v>3.681522</v>
+        <v>3.183416</v>
       </c>
     </row>
     <row r="540">
@@ -36017,7 +36017,7 @@
         </is>
       </c>
       <c r="H540" t="n">
-        <v>4218.299805</v>
+        <v>4254.899902</v>
       </c>
       <c r="I540" t="inlineStr">
         <is>
@@ -36045,7 +36045,7 @@
         </is>
       </c>
       <c r="N540" t="n">
-        <v>5.92888</v>
+        <v>6.465655</v>
       </c>
     </row>
     <row r="541">
@@ -36083,7 +36083,7 @@
         </is>
       </c>
       <c r="H541" t="n">
-        <v>4325.600098</v>
+        <v>4341.100098</v>
       </c>
       <c r="I541" t="inlineStr">
         <is>
@@ -36111,7 +36111,7 @@
         </is>
       </c>
       <c r="N541" t="n">
-        <v>2.543686</v>
+        <v>2.025904</v>
       </c>
     </row>
     <row r="542">
@@ -36149,7 +36149,7 @@
         </is>
       </c>
       <c r="H542" t="n">
-        <v>4713.899902</v>
+        <v>4745.100098</v>
       </c>
       <c r="I542" t="inlineStr">
         <is>
@@ -36177,7 +36177,7 @@
         </is>
       </c>
       <c r="N542" t="n">
-        <v>8.976785</v>
+        <v>9.306397</v>
       </c>
     </row>
     <row r="543">
@@ -36215,7 +36215,7 @@
         </is>
       </c>
       <c r="H543" t="n">
-        <v>5230.5</v>
+        <v>5247.899902</v>
       </c>
       <c r="I543" t="inlineStr">
         <is>
@@ -36243,7 +36243,7 @@
         </is>
       </c>
       <c r="N543" t="n">
-        <v>10.959081</v>
+        <v>10.59619</v>
       </c>
     </row>
     <row r="544">
@@ -36309,7 +36309,7 @@
         </is>
       </c>
       <c r="N544" t="n">
-        <v>-11.144248</v>
+        <v>-11.438858</v>
       </c>
     </row>
     <row r="545">
@@ -36347,7 +36347,7 @@
         </is>
       </c>
       <c r="H545" t="n">
-        <v>4614.700195</v>
+        <v>4629.600098</v>
       </c>
       <c r="I545" t="inlineStr">
         <is>
@@ -36375,7 +36375,7 @@
         </is>
       </c>
       <c r="N545" t="n">
-        <v>-0.70789</v>
+        <v>-0.387297</v>
       </c>
     </row>
     <row r="546">
@@ -36413,7 +36413,7 @@
         </is>
       </c>
       <c r="H546" t="n">
-        <v>4560.5</v>
+        <v>4593</v>
       </c>
       <c r="I546" t="inlineStr">
         <is>
@@ -36441,7 +36441,7 @@
         </is>
       </c>
       <c r="N546" t="n">
-        <v>-1.174512</v>
+        <v>-0.790567</v>
       </c>
     </row>
     <row r="547">
@@ -36479,7 +36479,7 @@
         </is>
       </c>
       <c r="H547" t="n">
-        <v>4022.899902</v>
+        <v>4038.5</v>
       </c>
       <c r="I547" t="inlineStr">
         <is>
@@ -36507,7 +36507,7 @@
         </is>
       </c>
       <c r="N547" t="n">
-        <v>-11.788183</v>
+        <v>-12.072719</v>
       </c>
     </row>
     <row r="548">
@@ -36545,7 +36545,7 @@
         </is>
       </c>
       <c r="H548" t="n">
-        <v>4049.100098</v>
+        <v>4107</v>
       </c>
       <c r="I548" t="inlineStr">
         <is>
@@ -36573,7 +36573,7 @@
         </is>
       </c>
       <c r="N548" t="n">
-        <v>0.651276</v>
+        <v>1.696174</v>
       </c>
     </row>
     <row r="549">
@@ -36611,7 +36611,7 @@
         </is>
       </c>
       <c r="H549" t="n">
-        <v>4431.100098</v>
+        <v>4481.5</v>
       </c>
       <c r="I549" t="inlineStr">
         <is>
@@ -36639,7 +36639,7 @@
         </is>
       </c>
       <c r="N549" t="n">
-        <v>9.434195000000001</v>
+        <v>9.118577999999999</v>
       </c>
     </row>
     <row r="550">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4331.600098</v>
+        <v>4329.299805</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-2.245492</v>
+        <v>-3.396189</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>107.419998</v>
+        <v>102.610001</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>18.70925</v>
+        <v>13.393749</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>102.970001</v>
+        <v>103.730003</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>20.067629</v>
+        <v>20.953826</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>109.68</v>
+        <v>109.540001</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>3.344957</v>
+        <v>3.213044</v>
       </c>
     </row>
     <row r="734">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7626.77002</v>
+        <v>7585.890137</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-0.772431</v>
+        <v>-1.304296</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>183.039993</v>
+        <v>182.539993</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>4.725938</v>
+        <v>4.439864</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1456</v>
+        <v>5.1546</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-0.878408</v>
+        <v>-0.705032</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51923.578125</v>
+        <v>51940.390625</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-2.373412</v>
+        <v>-2.341801</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9456</v>
+        <v>5.9476</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.065208</v>
+        <v>-1.031931</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>185959.625</v>
+        <v>185399.484375</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>4.813816</v>
+        <v>4.4981</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>440.839996</v>
+        <v>442.51001</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.893849</v>
+        <v>-1.522198</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>531.25</v>
+        <v>535</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>3.15534</v>
+        <v>3.883495</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26026.601562</v>
+        <v>26133.207031</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-1.305565</v>
+        <v>-0.9013099999999999</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4329.299805</v>
+        <v>4376.899902</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-3.396189</v>
+        <v>-2.334042</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>102.610001</v>
+        <v>106.949997</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>13.393749</v>
+        <v>18.189855</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>103.730003</v>
+        <v>103.169998</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>20.953826</v>
+        <v>20.300834</v>
       </c>
     </row>
     <row r="673">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1306.5</v>
+        <v>1320.25</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>2.4505</v>
+        <v>3.52872</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7585.890137</v>
+        <v>7600.680176</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-1.304296</v>
+        <v>-1.111871</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>182.539993</v>
+        <v>181.610001</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>4.439864</v>
+        <v>3.907771</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1546</v>
+        <v>5.1599</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-0.705032</v>
+        <v>-0.602936</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51940.390625</v>
+        <v>51741.929688</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-2.341801</v>
+        <v>-2.714947</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9476</v>
+        <v>5.9317</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.031931</v>
+        <v>-1.296501</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>185399.484375</v>
+        <v>184544.75</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>4.4981</v>
+        <v>4.01634</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>442.51001</v>
+        <v>444.839996</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.522198</v>
+        <v>-1.003674</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>3.883495</v>
+        <v>2.524272</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26133.207031</v>
+        <v>26407.919922</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-0.9013099999999999</v>
+        <v>0.140417</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4376.899902</v>
+        <v>4410.5</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-2.334042</v>
+        <v>-1.584291</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>106.949997</v>
+        <v>102.959999</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>18.189855</v>
+        <v>13.78053</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>103.169998</v>
+        <v>100.389999</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>20.300834</v>
+        <v>17.059231</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>109.540001</v>
+        <v>109.209999</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>3.213044</v>
+        <v>2.902103</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1320.25</v>
+        <v>1312.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>3.52872</v>
+        <v>2.920996</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7600.680176</v>
+        <v>7630.069824</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-1.111871</v>
+        <v>-0.729499</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N855"/>
+  <dimension ref="A1:N794"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>181.610001</v>
+        <v>182.089996</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>3.907771</v>
+        <v>4.182399</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1599</v>
+        <v>5.1563</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-0.602936</v>
+        <v>-0.6722860000000001</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51741.929688</v>
+        <v>51562.378906</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-2.714947</v>
+        <v>-3.052538</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9317</v>
+        <v>5.9081</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.296501</v>
+        <v>-1.689207</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>184544.75</v>
+        <v>184955.578125</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>4.01634</v>
+        <v>4.247898</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>444.839996</v>
+        <v>444.149994</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.003674</v>
+        <v>-1.15723</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>528</v>
+        <v>526.75</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>2.524272</v>
+        <v>2.281553</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26407.919922</v>
+        <v>26423.677734</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>0.140417</v>
+        <v>0.200172</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4410.5</v>
+        <v>4391</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-1.584291</v>
+        <v>-2.019413</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>102.959999</v>
+        <v>100.040001</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>13.78053</v>
+        <v>10.553656</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>100.389999</v>
+        <v>97.860001</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>17.059231</v>
+        <v>14.10914</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>109.209999</v>
+        <v>108.889999</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>2.902103</v>
+        <v>2.600586</v>
       </c>
     </row>
     <row r="734">
@@ -48791,22 +48791,22 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
@@ -48815,11 +48815,11 @@
         </is>
       </c>
       <c r="H734" t="n">
-        <v>1256</v>
+        <v>4307.540039</v>
       </c>
       <c r="I734" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J734" t="inlineStr">
@@ -48855,22 +48855,22 @@
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
@@ -48879,11 +48879,11 @@
         </is>
       </c>
       <c r="H735" t="n">
-        <v>1235.75</v>
+        <v>4605.379883</v>
       </c>
       <c r="I735" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J735" t="inlineStr">
@@ -48907,7 +48907,7 @@
         </is>
       </c>
       <c r="N735" t="n">
-        <v>-1.612261</v>
+        <v>6.914384</v>
       </c>
     </row>
     <row r="736">
@@ -48921,22 +48921,22 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
@@ -48945,11 +48945,11 @@
         </is>
       </c>
       <c r="H736" t="n">
-        <v>1217.25</v>
+        <v>4567</v>
       </c>
       <c r="I736" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J736" t="inlineStr">
@@ -48973,7 +48973,7 @@
         </is>
       </c>
       <c r="N736" t="n">
-        <v>-1.497067</v>
+        <v>-0.833371</v>
       </c>
     </row>
     <row r="737">
@@ -48987,22 +48987,22 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
@@ -49011,11 +49011,11 @@
         </is>
       </c>
       <c r="H737" t="n">
-        <v>1328.75</v>
+        <v>4766.180176</v>
       </c>
       <c r="I737" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J737" t="inlineStr">
@@ -49039,7 +49039,7 @@
         </is>
       </c>
       <c r="N737" t="n">
-        <v>9.159992000000001</v>
+        <v>4.361291</v>
       </c>
     </row>
     <row r="738">
@@ -49053,22 +49053,22 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
@@ -49077,11 +49077,11 @@
         </is>
       </c>
       <c r="H738" t="n">
-        <v>1490.5</v>
+        <v>4515.549805</v>
       </c>
       <c r="I738" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J738" t="inlineStr">
@@ -49105,7 +49105,7 @@
         </is>
       </c>
       <c r="N738" t="n">
-        <v>12.173095</v>
+        <v>-5.258517</v>
       </c>
     </row>
     <row r="739">
@@ -49119,22 +49119,22 @@
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G739" t="inlineStr">
@@ -49143,11 +49143,11 @@
         </is>
       </c>
       <c r="H739" t="n">
-        <v>1644.25</v>
+        <v>4373.939941</v>
       </c>
       <c r="I739" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J739" t="inlineStr">
@@ -49171,7 +49171,7 @@
         </is>
       </c>
       <c r="N739" t="n">
-        <v>10.31533</v>
+        <v>-3.136049</v>
       </c>
     </row>
     <row r="740">
@@ -49185,22 +49185,22 @@
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
@@ -49209,11 +49209,11 @@
         </is>
       </c>
       <c r="H740" t="n">
-        <v>1618.25</v>
+        <v>4530.410156</v>
       </c>
       <c r="I740" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J740" t="inlineStr">
@@ -49237,7 +49237,7 @@
         </is>
       </c>
       <c r="N740" t="n">
-        <v>-1.581268</v>
+        <v>3.577329</v>
       </c>
     </row>
     <row r="741">
@@ -49251,22 +49251,22 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G741" t="inlineStr">
@@ -49275,11 +49275,11 @@
         </is>
       </c>
       <c r="H741" t="n">
-        <v>1708.25</v>
+        <v>4131.930176</v>
       </c>
       <c r="I741" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J741" t="inlineStr">
@@ -49303,7 +49303,7 @@
         </is>
       </c>
       <c r="N741" t="n">
-        <v>5.561563</v>
+        <v>-8.795671</v>
       </c>
     </row>
     <row r="742">
@@ -49317,22 +49317,22 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G742" t="inlineStr">
@@ -49341,11 +49341,11 @@
         </is>
       </c>
       <c r="H742" t="n">
-        <v>1683.25</v>
+        <v>4132.149902</v>
       </c>
       <c r="I742" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J742" t="inlineStr">
@@ -49369,7 +49369,7 @@
         </is>
       </c>
       <c r="N742" t="n">
-        <v>-1.463486</v>
+        <v>0.005318</v>
       </c>
     </row>
     <row r="743">
@@ -49383,22 +49383,22 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G743" t="inlineStr">
@@ -49407,11 +49407,11 @@
         </is>
       </c>
       <c r="H743" t="n">
-        <v>1675</v>
+        <v>3785.379883</v>
       </c>
       <c r="I743" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J743" t="inlineStr">
@@ -49435,7 +49435,7 @@
         </is>
       </c>
       <c r="N743" t="n">
-        <v>-0.490123</v>
+        <v>-8.391999999999999</v>
       </c>
     </row>
     <row r="744">
@@ -49449,22 +49449,22 @@
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G744" t="inlineStr">
@@ -49473,11 +49473,11 @@
         </is>
       </c>
       <c r="H744" t="n">
-        <v>1637</v>
+        <v>4130.290039</v>
       </c>
       <c r="I744" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J744" t="inlineStr">
@@ -49501,7 +49501,7 @@
         </is>
       </c>
       <c r="N744" t="n">
-        <v>-2.268657</v>
+        <v>9.111639</v>
       </c>
     </row>
     <row r="745">
@@ -49515,22 +49515,22 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G745" t="inlineStr">
@@ -49539,11 +49539,11 @@
         </is>
       </c>
       <c r="H745" t="n">
-        <v>1507.5</v>
+        <v>3955</v>
       </c>
       <c r="I745" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J745" t="inlineStr">
@@ -49567,7 +49567,7 @@
         </is>
       </c>
       <c r="N745" t="n">
-        <v>-7.910812</v>
+        <v>-4.244013</v>
       </c>
     </row>
     <row r="746">
@@ -49581,22 +49581,22 @@
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G746" t="inlineStr">
@@ -49605,11 +49605,11 @@
         </is>
       </c>
       <c r="H746" t="n">
-        <v>1364.75</v>
+        <v>3585.620117</v>
       </c>
       <c r="I746" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J746" t="inlineStr">
@@ -49633,7 +49633,7 @@
         </is>
       </c>
       <c r="N746" t="n">
-        <v>-9.46932</v>
+        <v>-9.339567000000001</v>
       </c>
     </row>
     <row r="747">
@@ -49647,22 +49647,22 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G747" t="inlineStr">
@@ -49671,11 +49671,11 @@
         </is>
       </c>
       <c r="H747" t="n">
-        <v>1407</v>
+        <v>3871.97998</v>
       </c>
       <c r="I747" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J747" t="inlineStr">
@@ -49699,7 +49699,7 @@
         </is>
       </c>
       <c r="N747" t="n">
-        <v>3.095805</v>
+        <v>7.986341</v>
       </c>
     </row>
     <row r="748">
@@ -49713,22 +49713,22 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G748" t="inlineStr">
@@ -49737,11 +49737,11 @@
         </is>
       </c>
       <c r="H748" t="n">
-        <v>1469.5</v>
+        <v>4080.110107</v>
       </c>
       <c r="I748" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J748" t="inlineStr">
@@ -49765,7 +49765,7 @@
         </is>
       </c>
       <c r="N748" t="n">
-        <v>4.442075</v>
+        <v>5.375289</v>
       </c>
     </row>
     <row r="749">
@@ -49779,22 +49779,22 @@
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G749" t="inlineStr">
@@ -49803,11 +49803,11 @@
         </is>
       </c>
       <c r="H749" t="n">
-        <v>1519.25</v>
+        <v>3839.5</v>
       </c>
       <c r="I749" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J749" t="inlineStr">
@@ -49831,7 +49831,7 @@
         </is>
       </c>
       <c r="N749" t="n">
-        <v>3.385505</v>
+        <v>-5.897147</v>
       </c>
     </row>
     <row r="750">
@@ -49845,22 +49845,22 @@
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G750" t="inlineStr">
@@ -49869,11 +49869,11 @@
         </is>
       </c>
       <c r="H750" t="n">
-        <v>1538</v>
+        <v>4076.600098</v>
       </c>
       <c r="I750" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J750" t="inlineStr">
@@ -49897,7 +49897,7 @@
         </is>
       </c>
       <c r="N750" t="n">
-        <v>1.234162</v>
+        <v>6.175286</v>
       </c>
     </row>
     <row r="751">
@@ -49911,22 +49911,22 @@
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G751" t="inlineStr">
@@ -49935,11 +49935,11 @@
         </is>
       </c>
       <c r="H751" t="n">
-        <v>1490.5</v>
+        <v>3970.149902</v>
       </c>
       <c r="I751" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J751" t="inlineStr">
@@ -49963,7 +49963,7 @@
         </is>
       </c>
       <c r="N751" t="n">
-        <v>-3.088427</v>
+        <v>-2.611249</v>
       </c>
     </row>
     <row r="752">
@@ -49977,22 +49977,22 @@
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G752" t="inlineStr">
@@ -50001,11 +50001,11 @@
         </is>
       </c>
       <c r="H752" t="n">
-        <v>1505.5</v>
+        <v>4109.310059</v>
       </c>
       <c r="I752" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J752" t="inlineStr">
@@ -50029,7 +50029,7 @@
         </is>
       </c>
       <c r="N752" t="n">
-        <v>1.006374</v>
+        <v>3.505161</v>
       </c>
     </row>
     <row r="753">
@@ -50043,22 +50043,22 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G753" t="inlineStr">
@@ -50067,11 +50067,11 @@
         </is>
       </c>
       <c r="H753" t="n">
-        <v>1444.25</v>
+        <v>4169.47998</v>
       </c>
       <c r="I753" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J753" t="inlineStr">
@@ -50095,7 +50095,7 @@
         </is>
       </c>
       <c r="N753" t="n">
-        <v>-4.068416</v>
+        <v>1.464234</v>
       </c>
     </row>
     <row r="754">
@@ -50109,22 +50109,22 @@
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F754" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G754" t="inlineStr">
@@ -50133,11 +50133,11 @@
         </is>
       </c>
       <c r="H754" t="n">
-        <v>1299.75</v>
+        <v>4179.830078</v>
       </c>
       <c r="I754" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J754" t="inlineStr">
@@ -50161,7 +50161,7 @@
         </is>
       </c>
       <c r="N754" t="n">
-        <v>-10.005193</v>
+        <v>0.248235</v>
       </c>
     </row>
     <row r="755">
@@ -50175,22 +50175,22 @@
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G755" t="inlineStr">
@@ -50199,11 +50199,11 @@
         </is>
       </c>
       <c r="H755" t="n">
-        <v>1557.25</v>
+        <v>4450.379883</v>
       </c>
       <c r="I755" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J755" t="inlineStr">
@@ -50227,7 +50227,7 @@
         </is>
       </c>
       <c r="N755" t="n">
-        <v>19.811502</v>
+        <v>6.472746</v>
       </c>
     </row>
     <row r="756">
@@ -50241,22 +50241,22 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G756" t="inlineStr">
@@ -50265,11 +50265,11 @@
         </is>
       </c>
       <c r="H756" t="n">
-        <v>1445.75</v>
+        <v>4588.959961</v>
       </c>
       <c r="I756" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J756" t="inlineStr">
@@ -50293,7 +50293,7 @@
         </is>
       </c>
       <c r="N756" t="n">
-        <v>-7.160058</v>
+        <v>3.113893</v>
       </c>
     </row>
     <row r="757">
@@ -50307,22 +50307,22 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F757" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G757" t="inlineStr">
@@ -50331,11 +50331,11 @@
         </is>
       </c>
       <c r="H757" t="n">
-        <v>1360</v>
+        <v>4507.660156</v>
       </c>
       <c r="I757" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J757" t="inlineStr">
@@ -50359,7 +50359,7 @@
         </is>
       </c>
       <c r="N757" t="n">
-        <v>-5.931178</v>
+        <v>-1.771639</v>
       </c>
     </row>
     <row r="758">
@@ -50373,22 +50373,22 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G758" t="inlineStr">
@@ -50397,11 +50397,11 @@
         </is>
       </c>
       <c r="H758" t="n">
-        <v>1275</v>
+        <v>4288.049805</v>
       </c>
       <c r="I758" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J758" t="inlineStr">
@@ -50425,7 +50425,7 @@
         </is>
       </c>
       <c r="N758" t="n">
-        <v>-6.25</v>
+        <v>-4.871937</v>
       </c>
     </row>
     <row r="759">
@@ -50439,22 +50439,22 @@
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F759" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G759" t="inlineStr">
@@ -50463,11 +50463,11 @@
         </is>
       </c>
       <c r="H759" t="n">
-        <v>1287</v>
+        <v>4193.799805</v>
       </c>
       <c r="I759" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J759" t="inlineStr">
@@ -50491,7 +50491,7 @@
         </is>
       </c>
       <c r="N759" t="n">
-        <v>0.941176</v>
+        <v>-2.197969</v>
       </c>
     </row>
     <row r="760">
@@ -50505,22 +50505,22 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G760" t="inlineStr">
@@ -50529,11 +50529,11 @@
         </is>
       </c>
       <c r="H760" t="n">
-        <v>1342.75</v>
+        <v>4567.799805</v>
       </c>
       <c r="I760" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J760" t="inlineStr">
@@ -50557,7 +50557,7 @@
         </is>
       </c>
       <c r="N760" t="n">
-        <v>4.331779</v>
+        <v>8.917927000000001</v>
       </c>
     </row>
     <row r="761">
@@ -50571,22 +50571,22 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F761" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G761" t="inlineStr">
@@ -50595,11 +50595,11 @@
         </is>
       </c>
       <c r="H761" t="n">
-        <v>1293.5</v>
+        <v>4769.830078</v>
       </c>
       <c r="I761" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J761" t="inlineStr">
@@ -50623,7 +50623,7 @@
         </is>
       </c>
       <c r="N761" t="n">
-        <v>-3.667846</v>
+        <v>4.422923</v>
       </c>
     </row>
     <row r="762">
@@ -50637,22 +50637,22 @@
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F762" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G762" t="inlineStr">
@@ -50661,11 +50661,11 @@
         </is>
       </c>
       <c r="H762" t="n">
-        <v>1222.25</v>
+        <v>4845.649902</v>
       </c>
       <c r="I762" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J762" t="inlineStr">
@@ -50689,7 +50689,7 @@
         </is>
       </c>
       <c r="N762" t="n">
-        <v>-5.508311</v>
+        <v>1.589571</v>
       </c>
     </row>
     <row r="763">
@@ -50703,22 +50703,22 @@
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F763" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G763" t="inlineStr">
@@ -50727,11 +50727,11 @@
         </is>
       </c>
       <c r="H763" t="n">
-        <v>1128.25</v>
+        <v>5096.27002</v>
       </c>
       <c r="I763" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J763" t="inlineStr">
@@ -50755,7 +50755,7 @@
         </is>
       </c>
       <c r="N763" t="n">
-        <v>-7.690734</v>
+        <v>5.172064</v>
       </c>
     </row>
     <row r="764">
@@ -50769,22 +50769,22 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F764" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G764" t="inlineStr">
@@ -50793,11 +50793,11 @@
         </is>
       </c>
       <c r="H764" t="n">
-        <v>1191.5</v>
+        <v>5254.350098</v>
       </c>
       <c r="I764" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J764" t="inlineStr">
@@ -50821,7 +50821,7 @@
         </is>
       </c>
       <c r="N764" t="n">
-        <v>5.606027</v>
+        <v>3.101878</v>
       </c>
     </row>
     <row r="765">
@@ -50835,22 +50835,22 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G765" t="inlineStr">
@@ -50859,11 +50859,11 @@
         </is>
       </c>
       <c r="H765" t="n">
-        <v>1145.5</v>
+        <v>5035.689941</v>
       </c>
       <c r="I765" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J765" t="inlineStr">
@@ -50887,7 +50887,7 @@
         </is>
       </c>
       <c r="N765" t="n">
-        <v>-3.86068</v>
+        <v>-4.161507</v>
       </c>
     </row>
     <row r="766">
@@ -50901,22 +50901,22 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E766" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F766" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G766" t="inlineStr">
@@ -50925,11 +50925,11 @@
         </is>
       </c>
       <c r="H766" t="n">
-        <v>1205</v>
+        <v>5277.509766</v>
       </c>
       <c r="I766" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J766" t="inlineStr">
@@ -50953,7 +50953,7 @@
         </is>
       </c>
       <c r="N766" t="n">
-        <v>5.194238</v>
+        <v>4.802119</v>
       </c>
     </row>
     <row r="767">
@@ -50967,22 +50967,22 @@
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E767" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G767" t="inlineStr">
@@ -50991,11 +50991,11 @@
         </is>
       </c>
       <c r="H767" t="n">
-        <v>1150.5</v>
+        <v>5460.47998</v>
       </c>
       <c r="I767" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J767" t="inlineStr">
@@ -51019,7 +51019,7 @@
         </is>
       </c>
       <c r="N767" t="n">
-        <v>-4.522822</v>
+        <v>3.46698</v>
       </c>
     </row>
     <row r="768">
@@ -51033,22 +51033,22 @@
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F768" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G768" t="inlineStr">
@@ -51057,11 +51057,11 @@
         </is>
       </c>
       <c r="H768" t="n">
-        <v>1028.5</v>
+        <v>5522.299805</v>
       </c>
       <c r="I768" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J768" t="inlineStr">
@@ -51085,7 +51085,7 @@
         </is>
       </c>
       <c r="N768" t="n">
-        <v>-10.604085</v>
+        <v>1.132132</v>
       </c>
     </row>
     <row r="769">
@@ -51099,22 +51099,22 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G769" t="inlineStr">
@@ -51123,11 +51123,11 @@
         </is>
       </c>
       <c r="H769" t="n">
-        <v>982</v>
+        <v>5648.399902</v>
       </c>
       <c r="I769" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J769" t="inlineStr">
@@ -51151,7 +51151,7 @@
         </is>
       </c>
       <c r="N769" t="n">
-        <v>-4.521147</v>
+        <v>2.283471</v>
       </c>
     </row>
     <row r="770">
@@ -51165,22 +51165,22 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E770" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F770" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G770" t="inlineStr">
@@ -51189,11 +51189,11 @@
         </is>
       </c>
       <c r="H770" t="n">
-        <v>1057</v>
+        <v>5762.47998</v>
       </c>
       <c r="I770" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J770" t="inlineStr">
@@ -51217,7 +51217,7 @@
         </is>
       </c>
       <c r="N770" t="n">
-        <v>7.637475</v>
+        <v>2.019688</v>
       </c>
     </row>
     <row r="771">
@@ -51231,22 +51231,22 @@
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F771" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G771" t="inlineStr">
@@ -51255,11 +51255,11 @@
         </is>
       </c>
       <c r="H771" t="n">
-        <v>982.5</v>
+        <v>5705.450195</v>
       </c>
       <c r="I771" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J771" t="inlineStr">
@@ -51283,7 +51283,7 @@
         </is>
       </c>
       <c r="N771" t="n">
-        <v>-7.04825</v>
+        <v>-0.9896740000000001</v>
       </c>
     </row>
     <row r="772">
@@ -51297,22 +51297,22 @@
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F772" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G772" t="inlineStr">
@@ -51321,11 +51321,11 @@
         </is>
       </c>
       <c r="H772" t="n">
-        <v>989.5</v>
+        <v>6032.379883</v>
       </c>
       <c r="I772" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J772" t="inlineStr">
@@ -51349,7 +51349,7 @@
         </is>
       </c>
       <c r="N772" t="n">
-        <v>0.712468</v>
+        <v>5.73013</v>
       </c>
     </row>
     <row r="773">
@@ -51363,22 +51363,22 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F773" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G773" t="inlineStr">
@@ -51387,11 +51387,11 @@
         </is>
       </c>
       <c r="H773" t="n">
-        <v>998.25</v>
+        <v>5881.629883</v>
       </c>
       <c r="I773" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J773" t="inlineStr">
@@ -51415,7 +51415,7 @@
         </is>
       </c>
       <c r="N773" t="n">
-        <v>0.884285</v>
+        <v>-2.499014</v>
       </c>
     </row>
     <row r="774">
@@ -51429,22 +51429,22 @@
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G774" t="inlineStr">
@@ -51453,11 +51453,11 @@
         </is>
       </c>
       <c r="H774" t="n">
-        <v>1042</v>
+        <v>6040.529785</v>
       </c>
       <c r="I774" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J774" t="inlineStr">
@@ -51481,7 +51481,7 @@
         </is>
       </c>
       <c r="N774" t="n">
-        <v>4.38267</v>
+        <v>2.70163</v>
       </c>
     </row>
     <row r="775">
@@ -51495,22 +51495,22 @@
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F775" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G775" t="inlineStr">
@@ -51519,11 +51519,11 @@
         </is>
       </c>
       <c r="H775" t="n">
-        <v>1011.5</v>
+        <v>5954.5</v>
       </c>
       <c r="I775" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J775" t="inlineStr">
@@ -51547,7 +51547,7 @@
         </is>
       </c>
       <c r="N775" t="n">
-        <v>-2.927063</v>
+        <v>-1.424209</v>
       </c>
     </row>
     <row r="776">
@@ -51561,22 +51561,22 @@
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F776" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G776" t="inlineStr">
@@ -51585,11 +51585,11 @@
         </is>
       </c>
       <c r="H776" t="n">
-        <v>1014.75</v>
+        <v>5611.850098</v>
       </c>
       <c r="I776" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J776" t="inlineStr">
@@ -51613,7 +51613,7 @@
         </is>
       </c>
       <c r="N776" t="n">
-        <v>0.321305</v>
+        <v>-5.75447</v>
       </c>
     </row>
     <row r="777">
@@ -51627,22 +51627,22 @@
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F777" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G777" t="inlineStr">
@@ -51651,11 +51651,11 @@
         </is>
       </c>
       <c r="H777" t="n">
-        <v>1034.75</v>
+        <v>5569.060059</v>
       </c>
       <c r="I777" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J777" t="inlineStr">
@@ -51679,7 +51679,7 @@
         </is>
       </c>
       <c r="N777" t="n">
-        <v>1.970929</v>
+        <v>-0.762494</v>
       </c>
     </row>
     <row r="778">
@@ -51693,22 +51693,22 @@
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F778" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G778" t="inlineStr">
@@ -51717,11 +51717,11 @@
         </is>
       </c>
       <c r="H778" t="n">
-        <v>1041.75</v>
+        <v>5911.689941</v>
       </c>
       <c r="I778" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J778" t="inlineStr">
@@ -51745,7 +51745,7 @@
         </is>
       </c>
       <c r="N778" t="n">
-        <v>0.676492</v>
+        <v>6.152383</v>
       </c>
     </row>
     <row r="779">
@@ -51759,22 +51759,22 @@
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F779" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G779" t="inlineStr">
@@ -51783,11 +51783,11 @@
         </is>
       </c>
       <c r="H779" t="n">
-        <v>1024.25</v>
+        <v>6204.950195</v>
       </c>
       <c r="I779" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J779" t="inlineStr">
@@ -51811,7 +51811,7 @@
         </is>
       </c>
       <c r="N779" t="n">
-        <v>-1.679866</v>
+        <v>4.960684</v>
       </c>
     </row>
     <row r="780">
@@ -51825,22 +51825,22 @@
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F780" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G780" t="inlineStr">
@@ -51849,11 +51849,11 @@
         </is>
       </c>
       <c r="H780" t="n">
-        <v>961.75</v>
+        <v>6339.390137</v>
       </c>
       <c r="I780" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J780" t="inlineStr">
@@ -51877,7 +51877,7 @@
         </is>
       </c>
       <c r="N780" t="n">
-        <v>-6.102026</v>
+        <v>2.166656</v>
       </c>
     </row>
     <row r="781">
@@ -51891,22 +51891,22 @@
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F781" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G781" t="inlineStr">
@@ -51915,11 +51915,11 @@
         </is>
       </c>
       <c r="H781" t="n">
-        <v>1036.75</v>
+        <v>6460.259766</v>
       </c>
       <c r="I781" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J781" t="inlineStr">
@@ -51943,7 +51943,7 @@
         </is>
       </c>
       <c r="N781" t="n">
-        <v>7.798284</v>
+        <v>1.906644</v>
       </c>
     </row>
     <row r="782">
@@ -51957,22 +51957,22 @@
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F782" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G782" t="inlineStr">
@@ -51981,11 +51981,11 @@
         </is>
       </c>
       <c r="H782" t="n">
-        <v>1001.75</v>
+        <v>6688.459961</v>
       </c>
       <c r="I782" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J782" t="inlineStr">
@@ -52009,7 +52009,7 @@
         </is>
       </c>
       <c r="N782" t="n">
-        <v>-3.375934</v>
+        <v>3.532369</v>
       </c>
     </row>
     <row r="783">
@@ -52023,22 +52023,22 @@
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G783" t="inlineStr">
@@ -52047,11 +52047,11 @@
         </is>
       </c>
       <c r="H783" t="n">
-        <v>1099.75</v>
+        <v>6840.200195</v>
       </c>
       <c r="I783" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J783" t="inlineStr">
@@ -52075,7 +52075,7 @@
         </is>
       </c>
       <c r="N783" t="n">
-        <v>9.78288</v>
+        <v>2.268687</v>
       </c>
     </row>
     <row r="784">
@@ -52089,22 +52089,22 @@
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F784" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G784" t="inlineStr">
@@ -52113,11 +52113,11 @@
         </is>
       </c>
       <c r="H784" t="n">
-        <v>1137.75</v>
+        <v>6849.089844</v>
       </c>
       <c r="I784" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J784" t="inlineStr">
@@ -52141,7 +52141,7 @@
         </is>
       </c>
       <c r="N784" t="n">
-        <v>3.455331</v>
+        <v>0.129962</v>
       </c>
     </row>
     <row r="785">
@@ -52155,22 +52155,22 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F785" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G785" t="inlineStr">
@@ -52179,11 +52179,11 @@
         </is>
       </c>
       <c r="H785" t="n">
-        <v>1030.5</v>
+        <v>6845.5</v>
       </c>
       <c r="I785" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J785" t="inlineStr">
@@ -52207,7 +52207,7 @@
         </is>
       </c>
       <c r="N785" t="n">
-        <v>-9.426500000000001</v>
+        <v>-0.052413</v>
       </c>
     </row>
     <row r="786">
@@ -52221,22 +52221,22 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F786" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G786" t="inlineStr">
@@ -52245,11 +52245,11 @@
         </is>
       </c>
       <c r="H786" t="n">
-        <v>1064.25</v>
+        <v>6939.029785</v>
       </c>
       <c r="I786" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J786" t="inlineStr">
@@ -52273,7 +52273,7 @@
         </is>
       </c>
       <c r="N786" t="n">
-        <v>3.275109</v>
+        <v>1.366296</v>
       </c>
     </row>
     <row r="787">
@@ -52287,22 +52287,22 @@
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F787" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G787" t="inlineStr">
@@ -52311,11 +52311,11 @@
         </is>
       </c>
       <c r="H787" t="n">
-        <v>1157.25</v>
+        <v>6878.879883</v>
       </c>
       <c r="I787" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J787" t="inlineStr">
@@ -52339,7 +52339,7 @@
         </is>
       </c>
       <c r="N787" t="n">
-        <v>8.738548</v>
+        <v>-0.866834</v>
       </c>
     </row>
     <row r="788">
@@ -52353,22 +52353,22 @@
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F788" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G788" t="inlineStr">
@@ -52377,11 +52377,11 @@
         </is>
       </c>
       <c r="H788" t="n">
-        <v>1171</v>
+        <v>6528.52002</v>
       </c>
       <c r="I788" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J788" t="inlineStr">
@@ -52405,7 +52405,7 @@
         </is>
       </c>
       <c r="N788" t="n">
-        <v>1.188162</v>
+        <v>-5.093269</v>
       </c>
     </row>
     <row r="789">
@@ -52419,22 +52419,22 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F789" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G789" t="inlineStr">
@@ -52443,11 +52443,11 @@
         </is>
       </c>
       <c r="H789" t="n">
-        <v>1182</v>
+        <v>7209.009766</v>
       </c>
       <c r="I789" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J789" t="inlineStr">
@@ -52471,7 +52471,7 @@
         </is>
       </c>
       <c r="N789" t="n">
-        <v>0.939368</v>
+        <v>10.423339</v>
       </c>
     </row>
     <row r="790">
@@ -52485,22 +52485,22 @@
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F790" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G790" t="inlineStr">
@@ -52509,11 +52509,11 @@
         </is>
       </c>
       <c r="H790" t="n">
-        <v>1186.75</v>
+        <v>7580.060059</v>
       </c>
       <c r="I790" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J790" t="inlineStr">
@@ -52537,7 +52537,7 @@
         </is>
       </c>
       <c r="N790" t="n">
-        <v>0.401861</v>
+        <v>5.147036</v>
       </c>
     </row>
     <row r="791">
@@ -52551,22 +52551,22 @@
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G791" t="inlineStr">
@@ -52575,11 +52575,11 @@
         </is>
       </c>
       <c r="H791" t="n">
-        <v>1116.75</v>
+        <v>7499.359863</v>
       </c>
       <c r="I791" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J791" t="inlineStr">
@@ -52603,7 +52603,7 @@
         </is>
       </c>
       <c r="N791" t="n">
-        <v>-5.898462</v>
+        <v>-1.064638</v>
       </c>
     </row>
     <row r="792">
@@ -52617,22 +52617,22 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G792" t="inlineStr">
@@ -52641,11 +52641,11 @@
         </is>
       </c>
       <c r="H792" t="n">
-        <v>1172</v>
+        <v>7489.720215</v>
       </c>
       <c r="I792" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J792" t="inlineStr">
@@ -52669,7 +52669,7 @@
         </is>
       </c>
       <c r="N792" t="n">
-        <v>4.947392</v>
+        <v>-0.12854</v>
       </c>
     </row>
     <row r="793">
@@ -52683,22 +52683,22 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G793" t="inlineStr">
@@ -52707,11 +52707,11 @@
         </is>
       </c>
       <c r="H793" t="n">
-        <v>1275.25</v>
+        <v>7686.140137</v>
       </c>
       <c r="I793" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J793" t="inlineStr">
@@ -52735,7 +52735,7 @@
         </is>
       </c>
       <c r="N793" t="n">
-        <v>8.809727000000001</v>
+        <v>2.622527</v>
       </c>
     </row>
     <row r="794">
@@ -52749,22 +52749,22 @@
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="F794" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="G794" t="inlineStr">
@@ -52773,11 +52773,11 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1312.5</v>
+        <v>7623.669922</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="J794" t="inlineStr">
@@ -52801,4031 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>2.920996</v>
-      </c>
-    </row>
-    <row r="795">
-      <c r="A795" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="B795" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C795" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D795" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E795" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F795" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G795" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H795" t="n">
-        <v>4307.540039</v>
-      </c>
-      <c r="I795" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J795" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K795" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L795" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M795" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N795" t="inlineStr"/>
-    </row>
-    <row r="796">
-      <c r="A796" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="B796" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C796" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D796" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E796" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F796" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G796" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H796" t="n">
-        <v>4605.379883</v>
-      </c>
-      <c r="I796" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J796" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K796" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L796" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M796" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N796" t="n">
-        <v>6.914384</v>
-      </c>
-    </row>
-    <row r="797">
-      <c r="A797" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="B797" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C797" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D797" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E797" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F797" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G797" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H797" t="n">
-        <v>4567</v>
-      </c>
-      <c r="I797" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J797" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K797" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L797" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M797" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N797" t="n">
-        <v>-0.833371</v>
-      </c>
-    </row>
-    <row r="798">
-      <c r="A798" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B798" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C798" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D798" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E798" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F798" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G798" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H798" t="n">
-        <v>4766.180176</v>
-      </c>
-      <c r="I798" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J798" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K798" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L798" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M798" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N798" t="n">
-        <v>4.361291</v>
-      </c>
-    </row>
-    <row r="799">
-      <c r="A799" s="1" t="n">
-        <v>44592</v>
-      </c>
-      <c r="B799" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C799" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D799" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E799" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F799" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G799" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H799" t="n">
-        <v>4515.549805</v>
-      </c>
-      <c r="I799" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J799" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K799" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L799" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M799" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N799" t="n">
-        <v>-5.258517</v>
-      </c>
-    </row>
-    <row r="800">
-      <c r="A800" s="1" t="n">
-        <v>44620</v>
-      </c>
-      <c r="B800" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C800" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D800" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E800" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F800" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G800" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H800" t="n">
-        <v>4373.939941</v>
-      </c>
-      <c r="I800" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J800" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K800" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L800" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M800" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N800" t="n">
-        <v>-3.136049</v>
-      </c>
-    </row>
-    <row r="801">
-      <c r="A801" s="1" t="n">
-        <v>44651</v>
-      </c>
-      <c r="B801" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C801" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D801" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E801" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F801" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G801" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H801" t="n">
-        <v>4530.410156</v>
-      </c>
-      <c r="I801" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J801" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K801" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L801" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M801" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N801" t="n">
-        <v>3.577329</v>
-      </c>
-    </row>
-    <row r="802">
-      <c r="A802" s="1" t="n">
-        <v>44681</v>
-      </c>
-      <c r="B802" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C802" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D802" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E802" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F802" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G802" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H802" t="n">
-        <v>4131.930176</v>
-      </c>
-      <c r="I802" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J802" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K802" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L802" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M802" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N802" t="n">
-        <v>-8.795671</v>
-      </c>
-    </row>
-    <row r="803">
-      <c r="A803" s="1" t="n">
-        <v>44712</v>
-      </c>
-      <c r="B803" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C803" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D803" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E803" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F803" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G803" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H803" t="n">
-        <v>4132.149902</v>
-      </c>
-      <c r="I803" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J803" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K803" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L803" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M803" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N803" t="n">
-        <v>0.005318</v>
-      </c>
-    </row>
-    <row r="804">
-      <c r="A804" s="1" t="n">
-        <v>44742</v>
-      </c>
-      <c r="B804" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C804" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D804" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E804" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F804" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G804" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H804" t="n">
-        <v>3785.379883</v>
-      </c>
-      <c r="I804" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J804" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K804" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L804" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M804" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N804" t="n">
-        <v>-8.391999999999999</v>
-      </c>
-    </row>
-    <row r="805">
-      <c r="A805" s="1" t="n">
-        <v>44773</v>
-      </c>
-      <c r="B805" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C805" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D805" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E805" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F805" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G805" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H805" t="n">
-        <v>4130.290039</v>
-      </c>
-      <c r="I805" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J805" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K805" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L805" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M805" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N805" t="n">
-        <v>9.111639</v>
-      </c>
-    </row>
-    <row r="806">
-      <c r="A806" s="1" t="n">
-        <v>44804</v>
-      </c>
-      <c r="B806" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C806" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D806" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E806" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F806" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G806" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H806" t="n">
-        <v>3955</v>
-      </c>
-      <c r="I806" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J806" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K806" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L806" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M806" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N806" t="n">
-        <v>-4.244013</v>
-      </c>
-    </row>
-    <row r="807">
-      <c r="A807" s="1" t="n">
-        <v>44834</v>
-      </c>
-      <c r="B807" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C807" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D807" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E807" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F807" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G807" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H807" t="n">
-        <v>3585.620117</v>
-      </c>
-      <c r="I807" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J807" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K807" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L807" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M807" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N807" t="n">
-        <v>-9.339567000000001</v>
-      </c>
-    </row>
-    <row r="808">
-      <c r="A808" s="1" t="n">
-        <v>44865</v>
-      </c>
-      <c r="B808" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C808" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D808" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E808" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F808" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G808" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H808" t="n">
-        <v>3871.97998</v>
-      </c>
-      <c r="I808" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J808" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K808" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L808" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M808" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N808" t="n">
-        <v>7.986341</v>
-      </c>
-    </row>
-    <row r="809">
-      <c r="A809" s="1" t="n">
-        <v>44895</v>
-      </c>
-      <c r="B809" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C809" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D809" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E809" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F809" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G809" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H809" t="n">
-        <v>4080.110107</v>
-      </c>
-      <c r="I809" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J809" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K809" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L809" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M809" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N809" t="n">
-        <v>5.375289</v>
-      </c>
-    </row>
-    <row r="810">
-      <c r="A810" s="1" t="n">
-        <v>44926</v>
-      </c>
-      <c r="B810" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C810" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D810" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E810" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F810" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G810" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H810" t="n">
-        <v>3839.5</v>
-      </c>
-      <c r="I810" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J810" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K810" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L810" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M810" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N810" t="n">
-        <v>-5.897147</v>
-      </c>
-    </row>
-    <row r="811">
-      <c r="A811" s="1" t="n">
-        <v>44957</v>
-      </c>
-      <c r="B811" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C811" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D811" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E811" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F811" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G811" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H811" t="n">
-        <v>4076.600098</v>
-      </c>
-      <c r="I811" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J811" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K811" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L811" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M811" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N811" t="n">
-        <v>6.175286</v>
-      </c>
-    </row>
-    <row r="812">
-      <c r="A812" s="1" t="n">
-        <v>44985</v>
-      </c>
-      <c r="B812" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C812" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D812" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E812" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F812" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G812" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H812" t="n">
-        <v>3970.149902</v>
-      </c>
-      <c r="I812" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J812" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K812" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L812" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M812" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N812" t="n">
-        <v>-2.611249</v>
-      </c>
-    </row>
-    <row r="813">
-      <c r="A813" s="1" t="n">
-        <v>45016</v>
-      </c>
-      <c r="B813" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C813" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D813" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E813" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F813" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G813" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H813" t="n">
-        <v>4109.310059</v>
-      </c>
-      <c r="I813" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J813" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K813" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L813" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M813" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N813" t="n">
-        <v>3.505161</v>
-      </c>
-    </row>
-    <row r="814">
-      <c r="A814" s="1" t="n">
-        <v>45046</v>
-      </c>
-      <c r="B814" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C814" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D814" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E814" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F814" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G814" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H814" t="n">
-        <v>4169.47998</v>
-      </c>
-      <c r="I814" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J814" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K814" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L814" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M814" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N814" t="n">
-        <v>1.464234</v>
-      </c>
-    </row>
-    <row r="815">
-      <c r="A815" s="1" t="n">
-        <v>45077</v>
-      </c>
-      <c r="B815" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C815" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D815" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E815" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F815" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G815" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H815" t="n">
-        <v>4179.830078</v>
-      </c>
-      <c r="I815" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J815" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K815" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L815" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M815" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N815" t="n">
-        <v>0.248235</v>
-      </c>
-    </row>
-    <row r="816">
-      <c r="A816" s="1" t="n">
-        <v>45107</v>
-      </c>
-      <c r="B816" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C816" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D816" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E816" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F816" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G816" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H816" t="n">
-        <v>4450.379883</v>
-      </c>
-      <c r="I816" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J816" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K816" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L816" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M816" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N816" t="n">
-        <v>6.472746</v>
-      </c>
-    </row>
-    <row r="817">
-      <c r="A817" s="1" t="n">
-        <v>45138</v>
-      </c>
-      <c r="B817" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C817" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D817" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E817" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F817" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G817" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H817" t="n">
-        <v>4588.959961</v>
-      </c>
-      <c r="I817" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J817" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K817" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L817" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M817" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N817" t="n">
-        <v>3.113893</v>
-      </c>
-    </row>
-    <row r="818">
-      <c r="A818" s="1" t="n">
-        <v>45169</v>
-      </c>
-      <c r="B818" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C818" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D818" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E818" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F818" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G818" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H818" t="n">
-        <v>4507.660156</v>
-      </c>
-      <c r="I818" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J818" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K818" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L818" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M818" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N818" t="n">
-        <v>-1.771639</v>
-      </c>
-    </row>
-    <row r="819">
-      <c r="A819" s="1" t="n">
-        <v>45199</v>
-      </c>
-      <c r="B819" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C819" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D819" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E819" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F819" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G819" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H819" t="n">
-        <v>4288.049805</v>
-      </c>
-      <c r="I819" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J819" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K819" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L819" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M819" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N819" t="n">
-        <v>-4.871937</v>
-      </c>
-    </row>
-    <row r="820">
-      <c r="A820" s="1" t="n">
-        <v>45230</v>
-      </c>
-      <c r="B820" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C820" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D820" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E820" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F820" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G820" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H820" t="n">
-        <v>4193.799805</v>
-      </c>
-      <c r="I820" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J820" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K820" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L820" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M820" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N820" t="n">
-        <v>-2.197969</v>
-      </c>
-    </row>
-    <row r="821">
-      <c r="A821" s="1" t="n">
-        <v>45260</v>
-      </c>
-      <c r="B821" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C821" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D821" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E821" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F821" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G821" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H821" t="n">
-        <v>4567.799805</v>
-      </c>
-      <c r="I821" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J821" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K821" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L821" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M821" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N821" t="n">
-        <v>8.917927000000001</v>
-      </c>
-    </row>
-    <row r="822">
-      <c r="A822" s="1" t="n">
-        <v>45291</v>
-      </c>
-      <c r="B822" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C822" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D822" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E822" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F822" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G822" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H822" t="n">
-        <v>4769.830078</v>
-      </c>
-      <c r="I822" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J822" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K822" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L822" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M822" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N822" t="n">
-        <v>4.422923</v>
-      </c>
-    </row>
-    <row r="823">
-      <c r="A823" s="1" t="n">
-        <v>45322</v>
-      </c>
-      <c r="B823" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C823" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D823" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E823" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F823" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G823" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H823" t="n">
-        <v>4845.649902</v>
-      </c>
-      <c r="I823" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J823" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K823" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L823" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M823" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N823" t="n">
-        <v>1.589571</v>
-      </c>
-    </row>
-    <row r="824">
-      <c r="A824" s="1" t="n">
-        <v>45351</v>
-      </c>
-      <c r="B824" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C824" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D824" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E824" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F824" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G824" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H824" t="n">
-        <v>5096.27002</v>
-      </c>
-      <c r="I824" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J824" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K824" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L824" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M824" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N824" t="n">
-        <v>5.172064</v>
-      </c>
-    </row>
-    <row r="825">
-      <c r="A825" s="1" t="n">
-        <v>45382</v>
-      </c>
-      <c r="B825" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C825" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D825" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E825" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F825" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G825" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H825" t="n">
-        <v>5254.350098</v>
-      </c>
-      <c r="I825" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J825" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K825" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L825" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M825" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N825" t="n">
-        <v>3.101878</v>
-      </c>
-    </row>
-    <row r="826">
-      <c r="A826" s="1" t="n">
-        <v>45412</v>
-      </c>
-      <c r="B826" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C826" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D826" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E826" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F826" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G826" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H826" t="n">
-        <v>5035.689941</v>
-      </c>
-      <c r="I826" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J826" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K826" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L826" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M826" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N826" t="n">
-        <v>-4.161507</v>
-      </c>
-    </row>
-    <row r="827">
-      <c r="A827" s="1" t="n">
-        <v>45443</v>
-      </c>
-      <c r="B827" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C827" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D827" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E827" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F827" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G827" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H827" t="n">
-        <v>5277.509766</v>
-      </c>
-      <c r="I827" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J827" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K827" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L827" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M827" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N827" t="n">
-        <v>4.802119</v>
-      </c>
-    </row>
-    <row r="828">
-      <c r="A828" s="1" t="n">
-        <v>45473</v>
-      </c>
-      <c r="B828" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C828" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D828" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E828" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F828" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G828" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H828" t="n">
-        <v>5460.47998</v>
-      </c>
-      <c r="I828" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J828" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K828" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L828" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M828" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N828" t="n">
-        <v>3.46698</v>
-      </c>
-    </row>
-    <row r="829">
-      <c r="A829" s="1" t="n">
-        <v>45504</v>
-      </c>
-      <c r="B829" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C829" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D829" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E829" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F829" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G829" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H829" t="n">
-        <v>5522.299805</v>
-      </c>
-      <c r="I829" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J829" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K829" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L829" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M829" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N829" t="n">
-        <v>1.132132</v>
-      </c>
-    </row>
-    <row r="830">
-      <c r="A830" s="1" t="n">
-        <v>45535</v>
-      </c>
-      <c r="B830" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C830" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D830" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E830" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F830" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G830" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H830" t="n">
-        <v>5648.399902</v>
-      </c>
-      <c r="I830" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J830" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K830" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L830" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M830" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N830" t="n">
-        <v>2.283471</v>
-      </c>
-    </row>
-    <row r="831">
-      <c r="A831" s="1" t="n">
-        <v>45565</v>
-      </c>
-      <c r="B831" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C831" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D831" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E831" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F831" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G831" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H831" t="n">
-        <v>5762.47998</v>
-      </c>
-      <c r="I831" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J831" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K831" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L831" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M831" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N831" t="n">
-        <v>2.019688</v>
-      </c>
-    </row>
-    <row r="832">
-      <c r="A832" s="1" t="n">
-        <v>45596</v>
-      </c>
-      <c r="B832" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C832" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D832" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E832" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F832" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G832" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H832" t="n">
-        <v>5705.450195</v>
-      </c>
-      <c r="I832" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J832" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K832" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L832" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M832" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N832" t="n">
-        <v>-0.9896740000000001</v>
-      </c>
-    </row>
-    <row r="833">
-      <c r="A833" s="1" t="n">
-        <v>45626</v>
-      </c>
-      <c r="B833" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C833" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D833" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E833" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F833" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G833" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H833" t="n">
-        <v>6032.379883</v>
-      </c>
-      <c r="I833" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J833" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K833" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L833" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M833" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N833" t="n">
-        <v>5.73013</v>
-      </c>
-    </row>
-    <row r="834">
-      <c r="A834" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B834" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C834" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D834" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E834" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F834" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G834" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H834" t="n">
-        <v>5881.629883</v>
-      </c>
-      <c r="I834" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J834" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K834" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L834" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M834" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N834" t="n">
-        <v>-2.499014</v>
-      </c>
-    </row>
-    <row r="835">
-      <c r="A835" s="1" t="n">
-        <v>45688</v>
-      </c>
-      <c r="B835" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C835" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D835" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E835" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F835" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G835" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H835" t="n">
-        <v>6040.529785</v>
-      </c>
-      <c r="I835" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J835" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K835" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L835" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M835" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N835" t="n">
-        <v>2.70163</v>
-      </c>
-    </row>
-    <row r="836">
-      <c r="A836" s="1" t="n">
-        <v>45716</v>
-      </c>
-      <c r="B836" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C836" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D836" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E836" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F836" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G836" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H836" t="n">
-        <v>5954.5</v>
-      </c>
-      <c r="I836" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J836" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K836" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L836" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M836" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N836" t="n">
-        <v>-1.424209</v>
-      </c>
-    </row>
-    <row r="837">
-      <c r="A837" s="1" t="n">
-        <v>45747</v>
-      </c>
-      <c r="B837" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C837" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D837" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E837" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F837" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G837" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H837" t="n">
-        <v>5611.850098</v>
-      </c>
-      <c r="I837" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J837" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K837" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L837" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M837" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N837" t="n">
-        <v>-5.75447</v>
-      </c>
-    </row>
-    <row r="838">
-      <c r="A838" s="1" t="n">
-        <v>45777</v>
-      </c>
-      <c r="B838" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C838" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D838" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E838" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F838" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G838" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H838" t="n">
-        <v>5569.060059</v>
-      </c>
-      <c r="I838" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J838" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K838" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L838" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M838" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N838" t="n">
-        <v>-0.762494</v>
-      </c>
-    </row>
-    <row r="839">
-      <c r="A839" s="1" t="n">
-        <v>45808</v>
-      </c>
-      <c r="B839" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C839" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D839" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E839" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F839" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G839" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H839" t="n">
-        <v>5911.689941</v>
-      </c>
-      <c r="I839" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J839" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K839" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L839" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M839" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N839" t="n">
-        <v>6.152383</v>
-      </c>
-    </row>
-    <row r="840">
-      <c r="A840" s="1" t="n">
-        <v>45838</v>
-      </c>
-      <c r="B840" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C840" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D840" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E840" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F840" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G840" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H840" t="n">
-        <v>6204.950195</v>
-      </c>
-      <c r="I840" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J840" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K840" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L840" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M840" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N840" t="n">
-        <v>4.960684</v>
-      </c>
-    </row>
-    <row r="841">
-      <c r="A841" s="1" t="n">
-        <v>45869</v>
-      </c>
-      <c r="B841" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C841" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D841" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E841" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F841" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G841" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H841" t="n">
-        <v>6339.390137</v>
-      </c>
-      <c r="I841" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J841" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K841" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L841" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M841" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N841" t="n">
-        <v>2.166656</v>
-      </c>
-    </row>
-    <row r="842">
-      <c r="A842" s="1" t="n">
-        <v>45900</v>
-      </c>
-      <c r="B842" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C842" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D842" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E842" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F842" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G842" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H842" t="n">
-        <v>6460.259766</v>
-      </c>
-      <c r="I842" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J842" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K842" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L842" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M842" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N842" t="n">
-        <v>1.906644</v>
-      </c>
-    </row>
-    <row r="843">
-      <c r="A843" s="1" t="n">
-        <v>45930</v>
-      </c>
-      <c r="B843" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C843" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D843" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E843" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F843" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G843" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H843" t="n">
-        <v>6688.459961</v>
-      </c>
-      <c r="I843" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J843" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K843" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L843" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M843" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N843" t="n">
-        <v>3.532369</v>
-      </c>
-    </row>
-    <row r="844">
-      <c r="A844" s="1" t="n">
-        <v>45961</v>
-      </c>
-      <c r="B844" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C844" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D844" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E844" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F844" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G844" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H844" t="n">
-        <v>6840.200195</v>
-      </c>
-      <c r="I844" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J844" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K844" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L844" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M844" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N844" t="n">
-        <v>2.268687</v>
-      </c>
-    </row>
-    <row r="845">
-      <c r="A845" s="1" t="n">
-        <v>45991</v>
-      </c>
-      <c r="B845" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C845" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D845" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E845" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F845" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G845" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H845" t="n">
-        <v>6849.089844</v>
-      </c>
-      <c r="I845" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J845" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K845" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L845" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M845" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N845" t="n">
-        <v>0.129962</v>
-      </c>
-    </row>
-    <row r="846">
-      <c r="A846" s="1" t="n">
-        <v>46022</v>
-      </c>
-      <c r="B846" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C846" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D846" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E846" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F846" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G846" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H846" t="n">
-        <v>6845.5</v>
-      </c>
-      <c r="I846" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J846" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K846" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L846" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M846" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N846" t="n">
-        <v>-0.052413</v>
-      </c>
-    </row>
-    <row r="847">
-      <c r="A847" s="1" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B847" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C847" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D847" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E847" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F847" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G847" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H847" t="n">
-        <v>6939.029785</v>
-      </c>
-      <c r="I847" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J847" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K847" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L847" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M847" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N847" t="n">
-        <v>1.366296</v>
-      </c>
-    </row>
-    <row r="848">
-      <c r="A848" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B848" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C848" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D848" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E848" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F848" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G848" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H848" t="n">
-        <v>6878.879883</v>
-      </c>
-      <c r="I848" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J848" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K848" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L848" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M848" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N848" t="n">
-        <v>-0.866834</v>
-      </c>
-    </row>
-    <row r="849">
-      <c r="A849" s="1" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B849" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C849" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D849" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E849" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F849" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G849" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H849" t="n">
-        <v>6528.52002</v>
-      </c>
-      <c r="I849" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J849" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K849" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L849" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M849" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N849" t="n">
-        <v>-5.093269</v>
-      </c>
-    </row>
-    <row r="850">
-      <c r="A850" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="B850" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C850" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D850" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E850" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F850" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G850" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H850" t="n">
-        <v>7209.009766</v>
-      </c>
-      <c r="I850" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J850" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K850" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L850" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M850" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N850" t="n">
-        <v>10.423339</v>
-      </c>
-    </row>
-    <row r="851">
-      <c r="A851" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B851" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C851" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D851" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E851" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F851" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G851" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H851" t="n">
-        <v>7580.060059</v>
-      </c>
-      <c r="I851" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J851" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K851" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L851" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M851" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N851" t="n">
-        <v>5.147036</v>
-      </c>
-    </row>
-    <row r="852">
-      <c r="A852" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="B852" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C852" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D852" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E852" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F852" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G852" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H852" t="n">
-        <v>7499.359863</v>
-      </c>
-      <c r="I852" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J852" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K852" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L852" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M852" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N852" t="n">
-        <v>-1.064638</v>
-      </c>
-    </row>
-    <row r="853">
-      <c r="A853" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="B853" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C853" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D853" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E853" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F853" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G853" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H853" t="n">
-        <v>7489.720215</v>
-      </c>
-      <c r="I853" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J853" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K853" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L853" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M853" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N853" t="n">
-        <v>-0.12854</v>
-      </c>
-    </row>
-    <row r="854">
-      <c r="A854" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B854" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C854" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D854" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E854" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F854" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G854" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H854" t="n">
-        <v>7686.140137</v>
-      </c>
-      <c r="I854" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J854" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K854" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L854" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M854" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N854" t="n">
-        <v>2.622527</v>
-      </c>
-    </row>
-    <row r="855">
-      <c r="A855" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B855" t="inlineStr">
-        <is>
-          <t>Yahoo Finance via yfinance</t>
-        </is>
-      </c>
-      <c r="C855" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="D855" t="inlineStr">
-        <is>
-          <t>sp500</t>
-        </is>
-      </c>
-      <c r="E855" t="inlineStr">
-        <is>
-          <t>bolsa_internacional</t>
-        </is>
-      </c>
-      <c r="F855" t="inlineStr">
-        <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="G855" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H855" t="n">
-        <v>7630.069824</v>
-      </c>
-      <c r="I855" t="inlineStr">
-        <is>
-          <t>Índice S&amp;P 500.</t>
-        </is>
-      </c>
-      <c r="J855" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K855" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L855" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M855" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N855" t="n">
-        <v>-0.729499</v>
+        <v>-0.812764</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N794"/>
+  <dimension ref="A1:N855"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>182.089996</v>
+        <v>183.279999</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>4.182399</v>
+        <v>4.863257</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1563</v>
+        <v>5.1421</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-0.6722860000000001</v>
+        <v>-0.9458299999999999</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51562.378906</v>
+        <v>51682.640625</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-3.052538</v>
+        <v>-2.826422</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9081</v>
+        <v>5.9057</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.689207</v>
+        <v>-1.729141</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>184955.578125</v>
+        <v>185229</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>4.247898</v>
+        <v>4.402009</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>444.149994</v>
+        <v>442.600006</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.15723</v>
+        <v>-1.50217</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>526.75</v>
+        <v>527.5</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>2.281553</v>
+        <v>2.427184</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26423.677734</v>
+        <v>26522.539062</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>0.200172</v>
+        <v>0.57506</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4391</v>
+        <v>4424.899902</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-2.019413</v>
+        <v>-1.262972</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>100.040001</v>
+        <v>103.870003</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>10.553656</v>
+        <v>14.78617</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>97.860001</v>
+        <v>100.300003</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>14.10914</v>
+        <v>16.954292</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>108.889999</v>
+        <v>109.690002</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>2.600586</v>
+        <v>3.354382</v>
       </c>
     </row>
     <row r="734">
@@ -48791,22 +48791,22 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
@@ -48815,11 +48815,11 @@
         </is>
       </c>
       <c r="H734" t="n">
-        <v>4307.540039</v>
+        <v>1256</v>
       </c>
       <c r="I734" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J734" t="inlineStr">
@@ -48855,22 +48855,22 @@
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
@@ -48879,11 +48879,11 @@
         </is>
       </c>
       <c r="H735" t="n">
-        <v>4605.379883</v>
+        <v>1235.75</v>
       </c>
       <c r="I735" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J735" t="inlineStr">
@@ -48907,7 +48907,7 @@
         </is>
       </c>
       <c r="N735" t="n">
-        <v>6.914384</v>
+        <v>-1.612261</v>
       </c>
     </row>
     <row r="736">
@@ -48921,22 +48921,22 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
@@ -48945,11 +48945,11 @@
         </is>
       </c>
       <c r="H736" t="n">
-        <v>4567</v>
+        <v>1217.25</v>
       </c>
       <c r="I736" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J736" t="inlineStr">
@@ -48973,7 +48973,7 @@
         </is>
       </c>
       <c r="N736" t="n">
-        <v>-0.833371</v>
+        <v>-1.497067</v>
       </c>
     </row>
     <row r="737">
@@ -48987,22 +48987,22 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
@@ -49011,11 +49011,11 @@
         </is>
       </c>
       <c r="H737" t="n">
-        <v>4766.180176</v>
+        <v>1328.75</v>
       </c>
       <c r="I737" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J737" t="inlineStr">
@@ -49039,7 +49039,7 @@
         </is>
       </c>
       <c r="N737" t="n">
-        <v>4.361291</v>
+        <v>9.159992000000001</v>
       </c>
     </row>
     <row r="738">
@@ -49053,22 +49053,22 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
@@ -49077,11 +49077,11 @@
         </is>
       </c>
       <c r="H738" t="n">
-        <v>4515.549805</v>
+        <v>1490.5</v>
       </c>
       <c r="I738" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J738" t="inlineStr">
@@ -49105,7 +49105,7 @@
         </is>
       </c>
       <c r="N738" t="n">
-        <v>-5.258517</v>
+        <v>12.173095</v>
       </c>
     </row>
     <row r="739">
@@ -49119,22 +49119,22 @@
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G739" t="inlineStr">
@@ -49143,11 +49143,11 @@
         </is>
       </c>
       <c r="H739" t="n">
-        <v>4373.939941</v>
+        <v>1644.25</v>
       </c>
       <c r="I739" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J739" t="inlineStr">
@@ -49171,7 +49171,7 @@
         </is>
       </c>
       <c r="N739" t="n">
-        <v>-3.136049</v>
+        <v>10.31533</v>
       </c>
     </row>
     <row r="740">
@@ -49185,22 +49185,22 @@
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
@@ -49209,11 +49209,11 @@
         </is>
       </c>
       <c r="H740" t="n">
-        <v>4530.410156</v>
+        <v>1618.25</v>
       </c>
       <c r="I740" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J740" t="inlineStr">
@@ -49237,7 +49237,7 @@
         </is>
       </c>
       <c r="N740" t="n">
-        <v>3.577329</v>
+        <v>-1.581268</v>
       </c>
     </row>
     <row r="741">
@@ -49251,22 +49251,22 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G741" t="inlineStr">
@@ -49275,11 +49275,11 @@
         </is>
       </c>
       <c r="H741" t="n">
-        <v>4131.930176</v>
+        <v>1708.25</v>
       </c>
       <c r="I741" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J741" t="inlineStr">
@@ -49303,7 +49303,7 @@
         </is>
       </c>
       <c r="N741" t="n">
-        <v>-8.795671</v>
+        <v>5.561563</v>
       </c>
     </row>
     <row r="742">
@@ -49317,22 +49317,22 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G742" t="inlineStr">
@@ -49341,11 +49341,11 @@
         </is>
       </c>
       <c r="H742" t="n">
-        <v>4132.149902</v>
+        <v>1683.25</v>
       </c>
       <c r="I742" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J742" t="inlineStr">
@@ -49369,7 +49369,7 @@
         </is>
       </c>
       <c r="N742" t="n">
-        <v>0.005318</v>
+        <v>-1.463486</v>
       </c>
     </row>
     <row r="743">
@@ -49383,22 +49383,22 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G743" t="inlineStr">
@@ -49407,11 +49407,11 @@
         </is>
       </c>
       <c r="H743" t="n">
-        <v>3785.379883</v>
+        <v>1675</v>
       </c>
       <c r="I743" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J743" t="inlineStr">
@@ -49435,7 +49435,7 @@
         </is>
       </c>
       <c r="N743" t="n">
-        <v>-8.391999999999999</v>
+        <v>-0.490123</v>
       </c>
     </row>
     <row r="744">
@@ -49449,22 +49449,22 @@
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G744" t="inlineStr">
@@ -49473,11 +49473,11 @@
         </is>
       </c>
       <c r="H744" t="n">
-        <v>4130.290039</v>
+        <v>1637</v>
       </c>
       <c r="I744" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J744" t="inlineStr">
@@ -49501,7 +49501,7 @@
         </is>
       </c>
       <c r="N744" t="n">
-        <v>9.111639</v>
+        <v>-2.268657</v>
       </c>
     </row>
     <row r="745">
@@ -49515,22 +49515,22 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G745" t="inlineStr">
@@ -49539,11 +49539,11 @@
         </is>
       </c>
       <c r="H745" t="n">
-        <v>3955</v>
+        <v>1507.5</v>
       </c>
       <c r="I745" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J745" t="inlineStr">
@@ -49567,7 +49567,7 @@
         </is>
       </c>
       <c r="N745" t="n">
-        <v>-4.244013</v>
+        <v>-7.910812</v>
       </c>
     </row>
     <row r="746">
@@ -49581,22 +49581,22 @@
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G746" t="inlineStr">
@@ -49605,11 +49605,11 @@
         </is>
       </c>
       <c r="H746" t="n">
-        <v>3585.620117</v>
+        <v>1364.75</v>
       </c>
       <c r="I746" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J746" t="inlineStr">
@@ -49633,7 +49633,7 @@
         </is>
       </c>
       <c r="N746" t="n">
-        <v>-9.339567000000001</v>
+        <v>-9.46932</v>
       </c>
     </row>
     <row r="747">
@@ -49647,22 +49647,22 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G747" t="inlineStr">
@@ -49671,11 +49671,11 @@
         </is>
       </c>
       <c r="H747" t="n">
-        <v>3871.97998</v>
+        <v>1407</v>
       </c>
       <c r="I747" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J747" t="inlineStr">
@@ -49699,7 +49699,7 @@
         </is>
       </c>
       <c r="N747" t="n">
-        <v>7.986341</v>
+        <v>3.095805</v>
       </c>
     </row>
     <row r="748">
@@ -49713,22 +49713,22 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G748" t="inlineStr">
@@ -49737,11 +49737,11 @@
         </is>
       </c>
       <c r="H748" t="n">
-        <v>4080.110107</v>
+        <v>1469.5</v>
       </c>
       <c r="I748" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J748" t="inlineStr">
@@ -49765,7 +49765,7 @@
         </is>
       </c>
       <c r="N748" t="n">
-        <v>5.375289</v>
+        <v>4.442075</v>
       </c>
     </row>
     <row r="749">
@@ -49779,22 +49779,22 @@
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G749" t="inlineStr">
@@ -49803,11 +49803,11 @@
         </is>
       </c>
       <c r="H749" t="n">
-        <v>3839.5</v>
+        <v>1519.25</v>
       </c>
       <c r="I749" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J749" t="inlineStr">
@@ -49831,7 +49831,7 @@
         </is>
       </c>
       <c r="N749" t="n">
-        <v>-5.897147</v>
+        <v>3.385505</v>
       </c>
     </row>
     <row r="750">
@@ -49845,22 +49845,22 @@
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G750" t="inlineStr">
@@ -49869,11 +49869,11 @@
         </is>
       </c>
       <c r="H750" t="n">
-        <v>4076.600098</v>
+        <v>1538</v>
       </c>
       <c r="I750" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J750" t="inlineStr">
@@ -49897,7 +49897,7 @@
         </is>
       </c>
       <c r="N750" t="n">
-        <v>6.175286</v>
+        <v>1.234162</v>
       </c>
     </row>
     <row r="751">
@@ -49911,22 +49911,22 @@
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G751" t="inlineStr">
@@ -49935,11 +49935,11 @@
         </is>
       </c>
       <c r="H751" t="n">
-        <v>3970.149902</v>
+        <v>1490.5</v>
       </c>
       <c r="I751" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J751" t="inlineStr">
@@ -49963,7 +49963,7 @@
         </is>
       </c>
       <c r="N751" t="n">
-        <v>-2.611249</v>
+        <v>-3.088427</v>
       </c>
     </row>
     <row r="752">
@@ -49977,22 +49977,22 @@
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G752" t="inlineStr">
@@ -50001,11 +50001,11 @@
         </is>
       </c>
       <c r="H752" t="n">
-        <v>4109.310059</v>
+        <v>1505.5</v>
       </c>
       <c r="I752" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J752" t="inlineStr">
@@ -50029,7 +50029,7 @@
         </is>
       </c>
       <c r="N752" t="n">
-        <v>3.505161</v>
+        <v>1.006374</v>
       </c>
     </row>
     <row r="753">
@@ -50043,22 +50043,22 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G753" t="inlineStr">
@@ -50067,11 +50067,11 @@
         </is>
       </c>
       <c r="H753" t="n">
-        <v>4169.47998</v>
+        <v>1444.25</v>
       </c>
       <c r="I753" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J753" t="inlineStr">
@@ -50095,7 +50095,7 @@
         </is>
       </c>
       <c r="N753" t="n">
-        <v>1.464234</v>
+        <v>-4.068416</v>
       </c>
     </row>
     <row r="754">
@@ -50109,22 +50109,22 @@
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F754" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G754" t="inlineStr">
@@ -50133,11 +50133,11 @@
         </is>
       </c>
       <c r="H754" t="n">
-        <v>4179.830078</v>
+        <v>1299.75</v>
       </c>
       <c r="I754" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J754" t="inlineStr">
@@ -50161,7 +50161,7 @@
         </is>
       </c>
       <c r="N754" t="n">
-        <v>0.248235</v>
+        <v>-10.005193</v>
       </c>
     </row>
     <row r="755">
@@ -50175,22 +50175,22 @@
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G755" t="inlineStr">
@@ -50199,11 +50199,11 @@
         </is>
       </c>
       <c r="H755" t="n">
-        <v>4450.379883</v>
+        <v>1557.25</v>
       </c>
       <c r="I755" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J755" t="inlineStr">
@@ -50227,7 +50227,7 @@
         </is>
       </c>
       <c r="N755" t="n">
-        <v>6.472746</v>
+        <v>19.811502</v>
       </c>
     </row>
     <row r="756">
@@ -50241,22 +50241,22 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G756" t="inlineStr">
@@ -50265,11 +50265,11 @@
         </is>
       </c>
       <c r="H756" t="n">
-        <v>4588.959961</v>
+        <v>1445.75</v>
       </c>
       <c r="I756" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J756" t="inlineStr">
@@ -50293,7 +50293,7 @@
         </is>
       </c>
       <c r="N756" t="n">
-        <v>3.113893</v>
+        <v>-7.160058</v>
       </c>
     </row>
     <row r="757">
@@ -50307,22 +50307,22 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F757" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G757" t="inlineStr">
@@ -50331,11 +50331,11 @@
         </is>
       </c>
       <c r="H757" t="n">
-        <v>4507.660156</v>
+        <v>1360</v>
       </c>
       <c r="I757" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J757" t="inlineStr">
@@ -50359,7 +50359,7 @@
         </is>
       </c>
       <c r="N757" t="n">
-        <v>-1.771639</v>
+        <v>-5.931178</v>
       </c>
     </row>
     <row r="758">
@@ -50373,22 +50373,22 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G758" t="inlineStr">
@@ -50397,11 +50397,11 @@
         </is>
       </c>
       <c r="H758" t="n">
-        <v>4288.049805</v>
+        <v>1275</v>
       </c>
       <c r="I758" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J758" t="inlineStr">
@@ -50425,7 +50425,7 @@
         </is>
       </c>
       <c r="N758" t="n">
-        <v>-4.871937</v>
+        <v>-6.25</v>
       </c>
     </row>
     <row r="759">
@@ -50439,22 +50439,22 @@
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F759" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G759" t="inlineStr">
@@ -50463,11 +50463,11 @@
         </is>
       </c>
       <c r="H759" t="n">
-        <v>4193.799805</v>
+        <v>1287</v>
       </c>
       <c r="I759" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J759" t="inlineStr">
@@ -50491,7 +50491,7 @@
         </is>
       </c>
       <c r="N759" t="n">
-        <v>-2.197969</v>
+        <v>0.941176</v>
       </c>
     </row>
     <row r="760">
@@ -50505,22 +50505,22 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G760" t="inlineStr">
@@ -50529,11 +50529,11 @@
         </is>
       </c>
       <c r="H760" t="n">
-        <v>4567.799805</v>
+        <v>1342.75</v>
       </c>
       <c r="I760" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J760" t="inlineStr">
@@ -50557,7 +50557,7 @@
         </is>
       </c>
       <c r="N760" t="n">
-        <v>8.917927000000001</v>
+        <v>4.331779</v>
       </c>
     </row>
     <row r="761">
@@ -50571,22 +50571,22 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F761" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G761" t="inlineStr">
@@ -50595,11 +50595,11 @@
         </is>
       </c>
       <c r="H761" t="n">
-        <v>4769.830078</v>
+        <v>1293.5</v>
       </c>
       <c r="I761" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J761" t="inlineStr">
@@ -50623,7 +50623,7 @@
         </is>
       </c>
       <c r="N761" t="n">
-        <v>4.422923</v>
+        <v>-3.667846</v>
       </c>
     </row>
     <row r="762">
@@ -50637,22 +50637,22 @@
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F762" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G762" t="inlineStr">
@@ -50661,11 +50661,11 @@
         </is>
       </c>
       <c r="H762" t="n">
-        <v>4845.649902</v>
+        <v>1222.25</v>
       </c>
       <c r="I762" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J762" t="inlineStr">
@@ -50689,7 +50689,7 @@
         </is>
       </c>
       <c r="N762" t="n">
-        <v>1.589571</v>
+        <v>-5.508311</v>
       </c>
     </row>
     <row r="763">
@@ -50703,22 +50703,22 @@
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F763" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G763" t="inlineStr">
@@ -50727,11 +50727,11 @@
         </is>
       </c>
       <c r="H763" t="n">
-        <v>5096.27002</v>
+        <v>1128.25</v>
       </c>
       <c r="I763" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J763" t="inlineStr">
@@ -50755,7 +50755,7 @@
         </is>
       </c>
       <c r="N763" t="n">
-        <v>5.172064</v>
+        <v>-7.690734</v>
       </c>
     </row>
     <row r="764">
@@ -50769,22 +50769,22 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F764" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G764" t="inlineStr">
@@ -50793,11 +50793,11 @@
         </is>
       </c>
       <c r="H764" t="n">
-        <v>5254.350098</v>
+        <v>1191.5</v>
       </c>
       <c r="I764" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J764" t="inlineStr">
@@ -50821,7 +50821,7 @@
         </is>
       </c>
       <c r="N764" t="n">
-        <v>3.101878</v>
+        <v>5.606027</v>
       </c>
     </row>
     <row r="765">
@@ -50835,22 +50835,22 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G765" t="inlineStr">
@@ -50859,11 +50859,11 @@
         </is>
       </c>
       <c r="H765" t="n">
-        <v>5035.689941</v>
+        <v>1145.5</v>
       </c>
       <c r="I765" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J765" t="inlineStr">
@@ -50887,7 +50887,7 @@
         </is>
       </c>
       <c r="N765" t="n">
-        <v>-4.161507</v>
+        <v>-3.86068</v>
       </c>
     </row>
     <row r="766">
@@ -50901,22 +50901,22 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E766" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F766" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G766" t="inlineStr">
@@ -50925,11 +50925,11 @@
         </is>
       </c>
       <c r="H766" t="n">
-        <v>5277.509766</v>
+        <v>1205</v>
       </c>
       <c r="I766" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J766" t="inlineStr">
@@ -50953,7 +50953,7 @@
         </is>
       </c>
       <c r="N766" t="n">
-        <v>4.802119</v>
+        <v>5.194238</v>
       </c>
     </row>
     <row r="767">
@@ -50967,22 +50967,22 @@
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E767" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G767" t="inlineStr">
@@ -50991,11 +50991,11 @@
         </is>
       </c>
       <c r="H767" t="n">
-        <v>5460.47998</v>
+        <v>1150.5</v>
       </c>
       <c r="I767" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J767" t="inlineStr">
@@ -51019,7 +51019,7 @@
         </is>
       </c>
       <c r="N767" t="n">
-        <v>3.46698</v>
+        <v>-4.522822</v>
       </c>
     </row>
     <row r="768">
@@ -51033,22 +51033,22 @@
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F768" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G768" t="inlineStr">
@@ -51057,11 +51057,11 @@
         </is>
       </c>
       <c r="H768" t="n">
-        <v>5522.299805</v>
+        <v>1028.5</v>
       </c>
       <c r="I768" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J768" t="inlineStr">
@@ -51085,7 +51085,7 @@
         </is>
       </c>
       <c r="N768" t="n">
-        <v>1.132132</v>
+        <v>-10.604085</v>
       </c>
     </row>
     <row r="769">
@@ -51099,22 +51099,22 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G769" t="inlineStr">
@@ -51123,11 +51123,11 @@
         </is>
       </c>
       <c r="H769" t="n">
-        <v>5648.399902</v>
+        <v>982</v>
       </c>
       <c r="I769" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J769" t="inlineStr">
@@ -51151,7 +51151,7 @@
         </is>
       </c>
       <c r="N769" t="n">
-        <v>2.283471</v>
+        <v>-4.521147</v>
       </c>
     </row>
     <row r="770">
@@ -51165,22 +51165,22 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E770" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F770" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G770" t="inlineStr">
@@ -51189,11 +51189,11 @@
         </is>
       </c>
       <c r="H770" t="n">
-        <v>5762.47998</v>
+        <v>1057</v>
       </c>
       <c r="I770" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J770" t="inlineStr">
@@ -51217,7 +51217,7 @@
         </is>
       </c>
       <c r="N770" t="n">
-        <v>2.019688</v>
+        <v>7.637475</v>
       </c>
     </row>
     <row r="771">
@@ -51231,22 +51231,22 @@
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F771" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G771" t="inlineStr">
@@ -51255,11 +51255,11 @@
         </is>
       </c>
       <c r="H771" t="n">
-        <v>5705.450195</v>
+        <v>982.5</v>
       </c>
       <c r="I771" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J771" t="inlineStr">
@@ -51283,7 +51283,7 @@
         </is>
       </c>
       <c r="N771" t="n">
-        <v>-0.9896740000000001</v>
+        <v>-7.04825</v>
       </c>
     </row>
     <row r="772">
@@ -51297,22 +51297,22 @@
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F772" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G772" t="inlineStr">
@@ -51321,11 +51321,11 @@
         </is>
       </c>
       <c r="H772" t="n">
-        <v>6032.379883</v>
+        <v>989.5</v>
       </c>
       <c r="I772" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J772" t="inlineStr">
@@ -51349,7 +51349,7 @@
         </is>
       </c>
       <c r="N772" t="n">
-        <v>5.73013</v>
+        <v>0.712468</v>
       </c>
     </row>
     <row r="773">
@@ -51363,22 +51363,22 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F773" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G773" t="inlineStr">
@@ -51387,11 +51387,11 @@
         </is>
       </c>
       <c r="H773" t="n">
-        <v>5881.629883</v>
+        <v>998.25</v>
       </c>
       <c r="I773" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J773" t="inlineStr">
@@ -51415,7 +51415,7 @@
         </is>
       </c>
       <c r="N773" t="n">
-        <v>-2.499014</v>
+        <v>0.884285</v>
       </c>
     </row>
     <row r="774">
@@ -51429,22 +51429,22 @@
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G774" t="inlineStr">
@@ -51453,11 +51453,11 @@
         </is>
       </c>
       <c r="H774" t="n">
-        <v>6040.529785</v>
+        <v>1042</v>
       </c>
       <c r="I774" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J774" t="inlineStr">
@@ -51481,7 +51481,7 @@
         </is>
       </c>
       <c r="N774" t="n">
-        <v>2.70163</v>
+        <v>4.38267</v>
       </c>
     </row>
     <row r="775">
@@ -51495,22 +51495,22 @@
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F775" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G775" t="inlineStr">
@@ -51519,11 +51519,11 @@
         </is>
       </c>
       <c r="H775" t="n">
-        <v>5954.5</v>
+        <v>1011.5</v>
       </c>
       <c r="I775" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J775" t="inlineStr">
@@ -51547,7 +51547,7 @@
         </is>
       </c>
       <c r="N775" t="n">
-        <v>-1.424209</v>
+        <v>-2.927063</v>
       </c>
     </row>
     <row r="776">
@@ -51561,22 +51561,22 @@
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F776" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G776" t="inlineStr">
@@ -51585,11 +51585,11 @@
         </is>
       </c>
       <c r="H776" t="n">
-        <v>5611.850098</v>
+        <v>1014.75</v>
       </c>
       <c r="I776" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J776" t="inlineStr">
@@ -51613,7 +51613,7 @@
         </is>
       </c>
       <c r="N776" t="n">
-        <v>-5.75447</v>
+        <v>0.321305</v>
       </c>
     </row>
     <row r="777">
@@ -51627,22 +51627,22 @@
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F777" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G777" t="inlineStr">
@@ -51651,11 +51651,11 @@
         </is>
       </c>
       <c r="H777" t="n">
-        <v>5569.060059</v>
+        <v>1034.75</v>
       </c>
       <c r="I777" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J777" t="inlineStr">
@@ -51679,7 +51679,7 @@
         </is>
       </c>
       <c r="N777" t="n">
-        <v>-0.762494</v>
+        <v>1.970929</v>
       </c>
     </row>
     <row r="778">
@@ -51693,22 +51693,22 @@
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F778" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G778" t="inlineStr">
@@ -51717,11 +51717,11 @@
         </is>
       </c>
       <c r="H778" t="n">
-        <v>5911.689941</v>
+        <v>1041.75</v>
       </c>
       <c r="I778" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J778" t="inlineStr">
@@ -51745,7 +51745,7 @@
         </is>
       </c>
       <c r="N778" t="n">
-        <v>6.152383</v>
+        <v>0.676492</v>
       </c>
     </row>
     <row r="779">
@@ -51759,22 +51759,22 @@
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F779" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G779" t="inlineStr">
@@ -51783,11 +51783,11 @@
         </is>
       </c>
       <c r="H779" t="n">
-        <v>6204.950195</v>
+        <v>1024.25</v>
       </c>
       <c r="I779" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J779" t="inlineStr">
@@ -51811,7 +51811,7 @@
         </is>
       </c>
       <c r="N779" t="n">
-        <v>4.960684</v>
+        <v>-1.679866</v>
       </c>
     </row>
     <row r="780">
@@ -51825,22 +51825,22 @@
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F780" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G780" t="inlineStr">
@@ -51849,11 +51849,11 @@
         </is>
       </c>
       <c r="H780" t="n">
-        <v>6339.390137</v>
+        <v>961.75</v>
       </c>
       <c r="I780" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J780" t="inlineStr">
@@ -51877,7 +51877,7 @@
         </is>
       </c>
       <c r="N780" t="n">
-        <v>2.166656</v>
+        <v>-6.102026</v>
       </c>
     </row>
     <row r="781">
@@ -51891,22 +51891,22 @@
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F781" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G781" t="inlineStr">
@@ -51915,11 +51915,11 @@
         </is>
       </c>
       <c r="H781" t="n">
-        <v>6460.259766</v>
+        <v>1036.75</v>
       </c>
       <c r="I781" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J781" t="inlineStr">
@@ -51943,7 +51943,7 @@
         </is>
       </c>
       <c r="N781" t="n">
-        <v>1.906644</v>
+        <v>7.798284</v>
       </c>
     </row>
     <row r="782">
@@ -51957,22 +51957,22 @@
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F782" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G782" t="inlineStr">
@@ -51981,11 +51981,11 @@
         </is>
       </c>
       <c r="H782" t="n">
-        <v>6688.459961</v>
+        <v>1001.75</v>
       </c>
       <c r="I782" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J782" t="inlineStr">
@@ -52009,7 +52009,7 @@
         </is>
       </c>
       <c r="N782" t="n">
-        <v>3.532369</v>
+        <v>-3.375934</v>
       </c>
     </row>
     <row r="783">
@@ -52023,22 +52023,22 @@
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G783" t="inlineStr">
@@ -52047,11 +52047,11 @@
         </is>
       </c>
       <c r="H783" t="n">
-        <v>6840.200195</v>
+        <v>1099.75</v>
       </c>
       <c r="I783" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J783" t="inlineStr">
@@ -52075,7 +52075,7 @@
         </is>
       </c>
       <c r="N783" t="n">
-        <v>2.268687</v>
+        <v>9.78288</v>
       </c>
     </row>
     <row r="784">
@@ -52089,22 +52089,22 @@
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F784" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G784" t="inlineStr">
@@ -52113,11 +52113,11 @@
         </is>
       </c>
       <c r="H784" t="n">
-        <v>6849.089844</v>
+        <v>1137.75</v>
       </c>
       <c r="I784" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J784" t="inlineStr">
@@ -52141,7 +52141,7 @@
         </is>
       </c>
       <c r="N784" t="n">
-        <v>0.129962</v>
+        <v>3.455331</v>
       </c>
     </row>
     <row r="785">
@@ -52155,22 +52155,22 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F785" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G785" t="inlineStr">
@@ -52179,11 +52179,11 @@
         </is>
       </c>
       <c r="H785" t="n">
-        <v>6845.5</v>
+        <v>1030.5</v>
       </c>
       <c r="I785" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J785" t="inlineStr">
@@ -52207,7 +52207,7 @@
         </is>
       </c>
       <c r="N785" t="n">
-        <v>-0.052413</v>
+        <v>-9.426500000000001</v>
       </c>
     </row>
     <row r="786">
@@ -52221,22 +52221,22 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F786" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G786" t="inlineStr">
@@ -52245,11 +52245,11 @@
         </is>
       </c>
       <c r="H786" t="n">
-        <v>6939.029785</v>
+        <v>1064.25</v>
       </c>
       <c r="I786" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J786" t="inlineStr">
@@ -52273,7 +52273,7 @@
         </is>
       </c>
       <c r="N786" t="n">
-        <v>1.366296</v>
+        <v>3.275109</v>
       </c>
     </row>
     <row r="787">
@@ -52287,22 +52287,22 @@
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F787" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G787" t="inlineStr">
@@ -52311,11 +52311,11 @@
         </is>
       </c>
       <c r="H787" t="n">
-        <v>6878.879883</v>
+        <v>1157.25</v>
       </c>
       <c r="I787" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J787" t="inlineStr">
@@ -52339,7 +52339,7 @@
         </is>
       </c>
       <c r="N787" t="n">
-        <v>-0.866834</v>
+        <v>8.738548</v>
       </c>
     </row>
     <row r="788">
@@ -52353,22 +52353,22 @@
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F788" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G788" t="inlineStr">
@@ -52377,11 +52377,11 @@
         </is>
       </c>
       <c r="H788" t="n">
-        <v>6528.52002</v>
+        <v>1171</v>
       </c>
       <c r="I788" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J788" t="inlineStr">
@@ -52405,7 +52405,7 @@
         </is>
       </c>
       <c r="N788" t="n">
-        <v>-5.093269</v>
+        <v>1.188162</v>
       </c>
     </row>
     <row r="789">
@@ -52419,22 +52419,22 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F789" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G789" t="inlineStr">
@@ -52443,11 +52443,11 @@
         </is>
       </c>
       <c r="H789" t="n">
-        <v>7209.009766</v>
+        <v>1182</v>
       </c>
       <c r="I789" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J789" t="inlineStr">
@@ -52471,7 +52471,7 @@
         </is>
       </c>
       <c r="N789" t="n">
-        <v>10.423339</v>
+        <v>0.939368</v>
       </c>
     </row>
     <row r="790">
@@ -52485,22 +52485,22 @@
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F790" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G790" t="inlineStr">
@@ -52509,11 +52509,11 @@
         </is>
       </c>
       <c r="H790" t="n">
-        <v>7580.060059</v>
+        <v>1186.75</v>
       </c>
       <c r="I790" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J790" t="inlineStr">
@@ -52537,7 +52537,7 @@
         </is>
       </c>
       <c r="N790" t="n">
-        <v>5.147036</v>
+        <v>0.401861</v>
       </c>
     </row>
     <row r="791">
@@ -52551,22 +52551,22 @@
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G791" t="inlineStr">
@@ -52575,11 +52575,11 @@
         </is>
       </c>
       <c r="H791" t="n">
-        <v>7499.359863</v>
+        <v>1116.75</v>
       </c>
       <c r="I791" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J791" t="inlineStr">
@@ -52603,7 +52603,7 @@
         </is>
       </c>
       <c r="N791" t="n">
-        <v>-1.064638</v>
+        <v>-5.898462</v>
       </c>
     </row>
     <row r="792">
@@ -52617,22 +52617,22 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G792" t="inlineStr">
@@ -52641,11 +52641,11 @@
         </is>
       </c>
       <c r="H792" t="n">
-        <v>7489.720215</v>
+        <v>1172</v>
       </c>
       <c r="I792" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J792" t="inlineStr">
@@ -52669,7 +52669,7 @@
         </is>
       </c>
       <c r="N792" t="n">
-        <v>-0.12854</v>
+        <v>4.947392</v>
       </c>
     </row>
     <row r="793">
@@ -52683,22 +52683,22 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>ZS=F</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>futuro</t>
         </is>
       </c>
       <c r="G793" t="inlineStr">
@@ -52707,11 +52707,11 @@
         </is>
       </c>
       <c r="H793" t="n">
-        <v>7686.140137</v>
+        <v>1275.25</v>
       </c>
       <c r="I793" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Contrato futuro de soja.</t>
         </is>
       </c>
       <c r="J793" t="inlineStr">
@@ -52735,7 +52735,7 @@
         </is>
       </c>
       <c r="N793" t="n">
-        <v>2.622527</v>
+        <v>8.809727000000001</v>
       </c>
     </row>
     <row r="794">
@@ -52749,59 +52749,4083 @@
       </c>
       <c r="C794" t="inlineStr">
         <is>
+          <t>ZS=F</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>soja</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>commodities</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>futuro</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H794" t="n">
+        <v>1303.5</v>
+      </c>
+      <c r="I794" t="inlineStr">
+        <is>
+          <t>Contrato futuro de soja.</t>
+        </is>
+      </c>
+      <c r="J794" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L794" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M794" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N794" t="n">
+        <v>2.215252</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
           <t>^GSPC</t>
         </is>
       </c>
-      <c r="D794" t="inlineStr">
+      <c r="D795" t="inlineStr">
         <is>
           <t>sp500</t>
         </is>
       </c>
-      <c r="E794" t="inlineStr">
+      <c r="E795" t="inlineStr">
         <is>
           <t>bolsa_internacional</t>
         </is>
       </c>
-      <c r="F794" t="inlineStr">
+      <c r="F795" t="inlineStr">
         <is>
           <t>indice</t>
         </is>
       </c>
-      <c r="G794" t="inlineStr">
+      <c r="G795" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="H794" t="n">
-        <v>7623.669922</v>
-      </c>
-      <c r="I794" t="inlineStr">
+      <c r="H795" t="n">
+        <v>4307.540039</v>
+      </c>
+      <c r="I795" t="inlineStr">
         <is>
           <t>Índice S&amp;P 500.</t>
         </is>
       </c>
-      <c r="J794" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="K794" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="L794" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="M794" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="N794" t="n">
-        <v>-0.812764</v>
+      <c r="J795" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L795" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M795" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N795" t="inlineStr"/>
+    </row>
+    <row r="796">
+      <c r="A796" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H796" t="n">
+        <v>4605.379883</v>
+      </c>
+      <c r="I796" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J796" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L796" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M796" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N796" t="n">
+        <v>6.914384</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H797" t="n">
+        <v>4567</v>
+      </c>
+      <c r="I797" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J797" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K797" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L797" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M797" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N797" t="n">
+        <v>-0.833371</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="1" t="n">
+        <v>44561</v>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H798" t="n">
+        <v>4766.180176</v>
+      </c>
+      <c r="I798" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J798" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L798" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M798" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N798" t="n">
+        <v>4.361291</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="1" t="n">
+        <v>44592</v>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H799" t="n">
+        <v>4515.549805</v>
+      </c>
+      <c r="I799" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J799" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K799" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L799" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M799" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N799" t="n">
+        <v>-5.258517</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="1" t="n">
+        <v>44620</v>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H800" t="n">
+        <v>4373.939941</v>
+      </c>
+      <c r="I800" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J800" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L800" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M800" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N800" t="n">
+        <v>-3.136049</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" s="1" t="n">
+        <v>44651</v>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H801" t="n">
+        <v>4530.410156</v>
+      </c>
+      <c r="I801" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J801" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L801" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M801" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N801" t="n">
+        <v>3.577329</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="1" t="n">
+        <v>44681</v>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H802" t="n">
+        <v>4131.930176</v>
+      </c>
+      <c r="I802" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J802" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L802" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M802" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N802" t="n">
+        <v>-8.795671</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="1" t="n">
+        <v>44712</v>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H803" t="n">
+        <v>4132.149902</v>
+      </c>
+      <c r="I803" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J803" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K803" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L803" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M803" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N803" t="n">
+        <v>0.005318</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="1" t="n">
+        <v>44742</v>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H804" t="n">
+        <v>3785.379883</v>
+      </c>
+      <c r="I804" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J804" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K804" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L804" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M804" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N804" t="n">
+        <v>-8.391999999999999</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="1" t="n">
+        <v>44773</v>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H805" t="n">
+        <v>4130.290039</v>
+      </c>
+      <c r="I805" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J805" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L805" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M805" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N805" t="n">
+        <v>9.111639</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="1" t="n">
+        <v>44804</v>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H806" t="n">
+        <v>3955</v>
+      </c>
+      <c r="I806" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J806" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L806" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M806" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N806" t="n">
+        <v>-4.244013</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="1" t="n">
+        <v>44834</v>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H807" t="n">
+        <v>3585.620117</v>
+      </c>
+      <c r="I807" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J807" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K807" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L807" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M807" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N807" t="n">
+        <v>-9.339567000000001</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="1" t="n">
+        <v>44865</v>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H808" t="n">
+        <v>3871.97998</v>
+      </c>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J808" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K808" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L808" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M808" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N808" t="n">
+        <v>7.986341</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="1" t="n">
+        <v>44895</v>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H809" t="n">
+        <v>4080.110107</v>
+      </c>
+      <c r="I809" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J809" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L809" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M809" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N809" t="n">
+        <v>5.375289</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="1" t="n">
+        <v>44926</v>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H810" t="n">
+        <v>3839.5</v>
+      </c>
+      <c r="I810" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J810" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K810" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L810" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M810" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N810" t="n">
+        <v>-5.897147</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="1" t="n">
+        <v>44957</v>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H811" t="n">
+        <v>4076.600098</v>
+      </c>
+      <c r="I811" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J811" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K811" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L811" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M811" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N811" t="n">
+        <v>6.175286</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="1" t="n">
+        <v>44985</v>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H812" t="n">
+        <v>3970.149902</v>
+      </c>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J812" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K812" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L812" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M812" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N812" t="n">
+        <v>-2.611249</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="1" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H813" t="n">
+        <v>4109.310059</v>
+      </c>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J813" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K813" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L813" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M813" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N813" t="n">
+        <v>3.505161</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="1" t="n">
+        <v>45046</v>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H814" t="n">
+        <v>4169.47998</v>
+      </c>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J814" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L814" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M814" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N814" t="n">
+        <v>1.464234</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="1" t="n">
+        <v>45077</v>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H815" t="n">
+        <v>4179.830078</v>
+      </c>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J815" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L815" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M815" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N815" t="n">
+        <v>0.248235</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="1" t="n">
+        <v>45107</v>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H816" t="n">
+        <v>4450.379883</v>
+      </c>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J816" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L816" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M816" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N816" t="n">
+        <v>6.472746</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="1" t="n">
+        <v>45138</v>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H817" t="n">
+        <v>4588.959961</v>
+      </c>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J817" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L817" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M817" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N817" t="n">
+        <v>3.113893</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="1" t="n">
+        <v>45169</v>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H818" t="n">
+        <v>4507.660156</v>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J818" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L818" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M818" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N818" t="n">
+        <v>-1.771639</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="1" t="n">
+        <v>45199</v>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H819" t="n">
+        <v>4288.049805</v>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J819" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K819" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L819" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M819" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N819" t="n">
+        <v>-4.871937</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="1" t="n">
+        <v>45230</v>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H820" t="n">
+        <v>4193.799805</v>
+      </c>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J820" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L820" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M820" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N820" t="n">
+        <v>-2.197969</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="1" t="n">
+        <v>45260</v>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H821" t="n">
+        <v>4567.799805</v>
+      </c>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J821" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L821" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M821" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N821" t="n">
+        <v>8.917927000000001</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="1" t="n">
+        <v>45291</v>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H822" t="n">
+        <v>4769.830078</v>
+      </c>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J822" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K822" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L822" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M822" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N822" t="n">
+        <v>4.422923</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="1" t="n">
+        <v>45322</v>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H823" t="n">
+        <v>4845.649902</v>
+      </c>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J823" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L823" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M823" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N823" t="n">
+        <v>1.589571</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H824" t="n">
+        <v>5096.27002</v>
+      </c>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J824" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L824" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M824" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N824" t="n">
+        <v>5.172064</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="1" t="n">
+        <v>45382</v>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H825" t="n">
+        <v>5254.350098</v>
+      </c>
+      <c r="I825" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J825" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L825" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M825" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N825" t="n">
+        <v>3.101878</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="1" t="n">
+        <v>45412</v>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H826" t="n">
+        <v>5035.689941</v>
+      </c>
+      <c r="I826" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J826" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K826" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L826" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M826" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N826" t="n">
+        <v>-4.161507</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="1" t="n">
+        <v>45443</v>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H827" t="n">
+        <v>5277.509766</v>
+      </c>
+      <c r="I827" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J827" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L827" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M827" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N827" t="n">
+        <v>4.802119</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="1" t="n">
+        <v>45473</v>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H828" t="n">
+        <v>5460.47998</v>
+      </c>
+      <c r="I828" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J828" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L828" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M828" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N828" t="n">
+        <v>3.46698</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="1" t="n">
+        <v>45504</v>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H829" t="n">
+        <v>5522.299805</v>
+      </c>
+      <c r="I829" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J829" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L829" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M829" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N829" t="n">
+        <v>1.132132</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="1" t="n">
+        <v>45535</v>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H830" t="n">
+        <v>5648.399902</v>
+      </c>
+      <c r="I830" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J830" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K830" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L830" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M830" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N830" t="n">
+        <v>2.283471</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="1" t="n">
+        <v>45565</v>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H831" t="n">
+        <v>5762.47998</v>
+      </c>
+      <c r="I831" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J831" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L831" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M831" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N831" t="n">
+        <v>2.019688</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="1" t="n">
+        <v>45596</v>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H832" t="n">
+        <v>5705.450195</v>
+      </c>
+      <c r="I832" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J832" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K832" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L832" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M832" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N832" t="n">
+        <v>-0.9896740000000001</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="1" t="n">
+        <v>45626</v>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H833" t="n">
+        <v>6032.379883</v>
+      </c>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J833" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L833" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M833" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N833" t="n">
+        <v>5.73013</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="1" t="n">
+        <v>45657</v>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H834" t="n">
+        <v>5881.629883</v>
+      </c>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J834" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K834" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L834" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M834" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N834" t="n">
+        <v>-2.499014</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H835" t="n">
+        <v>6040.529785</v>
+      </c>
+      <c r="I835" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J835" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L835" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M835" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N835" t="n">
+        <v>2.70163</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="1" t="n">
+        <v>45716</v>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H836" t="n">
+        <v>5954.5</v>
+      </c>
+      <c r="I836" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J836" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L836" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M836" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N836" t="n">
+        <v>-1.424209</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="1" t="n">
+        <v>45747</v>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H837" t="n">
+        <v>5611.850098</v>
+      </c>
+      <c r="I837" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J837" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K837" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L837" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M837" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N837" t="n">
+        <v>-5.75447</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="1" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H838" t="n">
+        <v>5569.060059</v>
+      </c>
+      <c r="I838" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J838" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L838" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M838" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N838" t="n">
+        <v>-0.762494</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="1" t="n">
+        <v>45808</v>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H839" t="n">
+        <v>5911.689941</v>
+      </c>
+      <c r="I839" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J839" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L839" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M839" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N839" t="n">
+        <v>6.152383</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="1" t="n">
+        <v>45838</v>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H840" t="n">
+        <v>6204.950195</v>
+      </c>
+      <c r="I840" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J840" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L840" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M840" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N840" t="n">
+        <v>4.960684</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="1" t="n">
+        <v>45869</v>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H841" t="n">
+        <v>6339.390137</v>
+      </c>
+      <c r="I841" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J841" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L841" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M841" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N841" t="n">
+        <v>2.166656</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="1" t="n">
+        <v>45900</v>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H842" t="n">
+        <v>6460.259766</v>
+      </c>
+      <c r="I842" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J842" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K842" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L842" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M842" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N842" t="n">
+        <v>1.906644</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="1" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H843" t="n">
+        <v>6688.459961</v>
+      </c>
+      <c r="I843" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J843" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K843" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L843" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M843" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N843" t="n">
+        <v>3.532369</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="1" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H844" t="n">
+        <v>6840.200195</v>
+      </c>
+      <c r="I844" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J844" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K844" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L844" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M844" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N844" t="n">
+        <v>2.268687</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H845" t="n">
+        <v>6849.089844</v>
+      </c>
+      <c r="I845" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J845" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L845" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M845" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N845" t="n">
+        <v>0.129962</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H846" t="n">
+        <v>6845.5</v>
+      </c>
+      <c r="I846" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J846" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K846" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L846" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M846" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N846" t="n">
+        <v>-0.052413</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H847" t="n">
+        <v>6939.029785</v>
+      </c>
+      <c r="I847" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J847" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K847" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L847" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M847" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N847" t="n">
+        <v>1.366296</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H848" t="n">
+        <v>6878.879883</v>
+      </c>
+      <c r="I848" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J848" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L848" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M848" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N848" t="n">
+        <v>-0.866834</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H849" t="n">
+        <v>6528.52002</v>
+      </c>
+      <c r="I849" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J849" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L849" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M849" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N849" t="n">
+        <v>-5.093269</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H850" t="n">
+        <v>7209.009766</v>
+      </c>
+      <c r="I850" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J850" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K850" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L850" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M850" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N850" t="n">
+        <v>10.423339</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H851" t="n">
+        <v>7580.060059</v>
+      </c>
+      <c r="I851" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J851" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K851" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L851" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M851" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N851" t="n">
+        <v>5.147036</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H852" t="n">
+        <v>7499.359863</v>
+      </c>
+      <c r="I852" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J852" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K852" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L852" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M852" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N852" t="n">
+        <v>-1.064638</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H853" t="n">
+        <v>7489.720215</v>
+      </c>
+      <c r="I853" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J853" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K853" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L853" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M853" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N853" t="n">
+        <v>-0.12854</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H854" t="n">
+        <v>7686.140137</v>
+      </c>
+      <c r="I854" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J854" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K854" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L854" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M854" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N854" t="n">
+        <v>2.622527</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H855" t="n">
+        <v>7650.5</v>
+      </c>
+      <c r="I855" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="J855" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="L855" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="M855" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="N855" t="n">
+        <v>-0.463694</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>183.279999</v>
+        <v>182.470001</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>4.863257</v>
+        <v>4.399818</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1421</v>
+        <v>5.1442</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-0.9458299999999999</v>
+        <v>-0.905377</v>
       </c>
     </row>
     <row r="124">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>442.600006</v>
+        <v>443.5</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.50217</v>
+        <v>-1.301882</v>
       </c>
     </row>
     <row r="368">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>103.870003</v>
+        <v>99.290001</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>14.78617</v>
+        <v>9.724835000000001</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>100.300003</v>
+        <v>96.08000199999999</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>16.954292</v>
+        <v>12.033581</v>
       </c>
     </row>
     <row r="673">

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>182.470001</v>
+        <v>183.380005</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>4.399818</v>
+        <v>4.920475</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1442</v>
+        <v>5.1019</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-0.905377</v>
+        <v>-1.720213</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51682.640625</v>
+        <v>51959.019531</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-2.826422</v>
+        <v>-2.306775</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9057</v>
+        <v>5.8593</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.729141</v>
+        <v>-2.501239</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>185229</v>
+        <v>186247.09375</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>4.402009</v>
+        <v>4.975845</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>443.5</v>
+        <v>446.429993</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.301882</v>
+        <v>-0.649831</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>527.5</v>
+        <v>542.5</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>2.427184</v>
+        <v>5.339806</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26522.539062</v>
+        <v>27005.107422</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>0.57506</v>
+        <v>2.404988</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4424.899902</v>
+        <v>4386.200195</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-1.262972</v>
+        <v>-2.126516</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>99.290001</v>
+        <v>96.199997</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>9.724835000000001</v>
+        <v>6.310089</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>96.08000199999999</v>
+        <v>92.339996</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>12.033581</v>
+        <v>7.672568</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>109.690002</v>
+        <v>111.540001</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>3.354382</v>
+        <v>5.097525</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1303.5</v>
+        <v>1325.25</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>2.215252</v>
+        <v>3.9208</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7650.5</v>
+        <v>7743.27002</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-0.463694</v>
+        <v>0.7432839999999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>183.380005</v>
+        <v>183.190002</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>4.920475</v>
+        <v>4.811765</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1019</v>
+        <v>5.1202</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-1.720213</v>
+        <v>-1.367692</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51959.019531</v>
+        <v>51857.640625</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-2.306775</v>
+        <v>-2.497387</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8593</v>
+        <v>5.8591</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-2.501239</v>
+        <v>-2.504571</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>186247.09375</v>
+        <v>185986.109375</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>4.975845</v>
+        <v>4.828744</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>446.429993</v>
+        <v>449.369995</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-0.649831</v>
+        <v>0.004448</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>542.5</v>
+        <v>538.25</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>5.339806</v>
+        <v>4.514563</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>27005.107422</v>
+        <v>27251.701172</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>2.404988</v>
+        <v>3.340086</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4386.200195</v>
+        <v>4367.5</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-2.126516</v>
+        <v>-2.543791</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>96.199997</v>
+        <v>99.470001</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>6.310089</v>
+        <v>9.923752</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>92.339996</v>
+        <v>90.910004</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>7.672568</v>
+        <v>6.005132</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>111.540001</v>
+        <v>111.32</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>5.097525</v>
+        <v>4.890231</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1325.25</v>
+        <v>1327.25</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>3.9208</v>
+        <v>4.077632</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7743.27002</v>
+        <v>7770.220215</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>0.7432839999999999</v>
+        <v>1.093918</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>183.190002</v>
+        <v>182.740005</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>4.811765</v>
+        <v>4.554301</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1202</v>
+        <v>5.1167</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-1.367692</v>
+        <v>-1.435113</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51857.640625</v>
+        <v>51828.691406</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-2.497387</v>
+        <v>-2.551817</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8591</v>
+        <v>5.858</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-2.504571</v>
+        <v>-2.522876</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>185986.109375</v>
+        <v>185576.765625</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>4.828744</v>
+        <v>4.598023</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>449.369995</v>
+        <v>449.450012</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>0.004448</v>
+        <v>0.022256</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>538.25</v>
+        <v>538</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>4.514563</v>
+        <v>4.466019</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>27251.701172</v>
+        <v>27249.957031</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>3.340086</v>
+        <v>3.333473</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4367.5</v>
+        <v>4366</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-2.543791</v>
+        <v>-2.577262</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>99.470001</v>
+        <v>99.25</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>9.923752</v>
+        <v>9.680630000000001</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>90.910004</v>
+        <v>90.699997</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>6.005132</v>
+        <v>5.760255</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>111.32</v>
+        <v>111.169998</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>4.890231</v>
+        <v>4.748894</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1327.25</v>
+        <v>1327.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>4.077632</v>
+        <v>4.097236</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7770.220215</v>
+        <v>7768.72998</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>1.093918</v>
+        <v>1.07453</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>182.740005</v>
+        <v>184.679993</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>4.554301</v>
+        <v>5.66426</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1167</v>
+        <v>5.1471</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-1.435113</v>
+        <v>-0.849511</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51828.691406</v>
+        <v>51787.929688</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-2.551817</v>
+        <v>-2.628458</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.858</v>
+        <v>5.8651</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-2.522876</v>
+        <v>-2.40473</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>185576.765625</v>
+        <v>187575.046875</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>4.598023</v>
+        <v>5.724329</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>449.450012</v>
+        <v>448.869995</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>0.022256</v>
+        <v>-0.106823</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>538</v>
+        <v>528.75</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>4.466019</v>
+        <v>2.669903</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>27249.957031</v>
+        <v>26969.003906</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>3.333473</v>
+        <v>2.268081</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4366</v>
+        <v>4315.5</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-2.577262</v>
+        <v>-3.704117</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>99.25</v>
+        <v>97.620003</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>9.680630000000001</v>
+        <v>7.879329</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>90.699997</v>
+        <v>92.099998</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>5.760255</v>
+        <v>7.392719</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>111.169998</v>
+        <v>111.980003</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>4.748894</v>
+        <v>5.512114</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1327.5</v>
+        <v>1315.75</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>4.097236</v>
+        <v>3.175848</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7768.72998</v>
+        <v>7725.299805</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>1.07453</v>
+        <v>0.509484</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>184.679993</v>
+        <v>182.5</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>5.66426</v>
+        <v>4.416982</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1471</v>
+        <v>5.1764</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-0.849511</v>
+        <v>-0.28509</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51787.929688</v>
+        <v>51308.679688</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-2.628458</v>
+        <v>-3.529542</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8651</v>
+        <v>5.8909</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-2.40473</v>
+        <v>-1.975415</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>187575.046875</v>
+        <v>185430.703125</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>5.724329</v>
+        <v>4.515696</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>448.869995</v>
+        <v>449.720001</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-0.106823</v>
+        <v>0.08234</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>528.75</v>
+        <v>527.75</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>2.669903</v>
+        <v>2.475728</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26969.003906</v>
+        <v>26805.265625</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>2.268081</v>
+        <v>1.647176</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4315.5</v>
+        <v>4298.899902</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-3.704117</v>
+        <v>-4.074531</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>97.620003</v>
+        <v>100.309998</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>7.879329</v>
+        <v>10.852028</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>92.099998</v>
+        <v>94.66999800000001</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>7.392719</v>
+        <v>10.389454</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>111.980003</v>
+        <v>110.760002</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>5.512114</v>
+        <v>4.362579</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1315.75</v>
+        <v>1316</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>3.175848</v>
+        <v>3.195452</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7725.299805</v>
+        <v>7687.310059</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>0.509484</v>
+        <v>0.015221</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>182.5</v>
+        <v>182.770004</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>4.416982</v>
+        <v>4.571464</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1764</v>
+        <v>5.1808</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-0.28509</v>
+        <v>-0.200336</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51308.679688</v>
+        <v>51309.371094</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-3.529542</v>
+        <v>-3.528242</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8909</v>
+        <v>5.8912</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.975415</v>
+        <v>-1.970424</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>185430.703125</v>
+        <v>185707.59375</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>4.515696</v>
+        <v>4.671762</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>449.720001</v>
+        <v>449.549988</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>0.08234</v>
+        <v>0.044505</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>527.75</v>
+        <v>530</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>2.475728</v>
+        <v>2.912621</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26805.265625</v>
+        <v>26794.8125</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>1.647176</v>
+        <v>1.607537</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4298.899902</v>
+        <v>4296.299805</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-4.074531</v>
+        <v>-4.132549</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>100.309998</v>
+        <v>100.32</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>10.852028</v>
+        <v>10.863081</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>94.66999800000001</v>
+        <v>94.720001</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>10.389454</v>
+        <v>10.44776</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>110.760002</v>
+        <v>110.959999</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>4.362579</v>
+        <v>4.551024</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1316</v>
+        <v>1317.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>3.195452</v>
+        <v>3.313076</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7687.310059</v>
+        <v>7687.410156</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>0.015221</v>
+        <v>0.016524</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>182.770004</v>
+        <v>179.610001</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>4.571464</v>
+        <v>2.763475</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1808</v>
+        <v>5.204</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-0.200336</v>
+        <v>0.246575</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51309.371094</v>
+        <v>51492.351562</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-3.528242</v>
+        <v>-3.184203</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8912</v>
+        <v>5.9357</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.970424</v>
+        <v>-1.229946</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>185707.59375</v>
+        <v>182428.5</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>4.671762</v>
+        <v>2.823542</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>449.549988</v>
+        <v>453.279999</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>0.044505</v>
+        <v>0.874595</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>530</v>
+        <v>521.25</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>2.912621</v>
+        <v>1.213592</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26794.8125</v>
+        <v>26965.560547</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>1.607537</v>
+        <v>2.255024</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4296.299805</v>
+        <v>4306.899902</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-4.132549</v>
+        <v>-3.896019</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>100.32</v>
+        <v>99.589996</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>10.863081</v>
+        <v>10.056358</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>94.720001</v>
+        <v>94.099998</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>10.44776</v>
+        <v>9.724809</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>110.959999</v>
+        <v>109.449997</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>4.551024</v>
+        <v>3.128239</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1317.5</v>
+        <v>1305</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>3.313076</v>
+        <v>2.332876</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7687.410156</v>
+        <v>7712.609863</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>0.016524</v>
+        <v>0.344383</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>179.610001</v>
+        <v>180.869995</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2.763475</v>
+        <v>3.484378</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.204</v>
+        <v>5.1866</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0.246575</v>
+        <v>-0.088603</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51492.351562</v>
+        <v>51828.621094</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-3.184203</v>
+        <v>-2.55195</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9357</v>
+        <v>5.9081</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.229946</v>
+        <v>-1.689207</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>182428.5</v>
+        <v>183477</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>2.823542</v>
+        <v>3.414516</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>453.279999</v>
+        <v>451.149994</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>0.874595</v>
+        <v>0.400576</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>521.25</v>
+        <v>528.25</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>1.213592</v>
+        <v>2.572816</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26965.560547</v>
+        <v>27068.720703</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>2.255024</v>
+        <v>2.646214</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4306.899902</v>
+        <v>4321.200195</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-3.896019</v>
+        <v>-3.576923</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>99.589996</v>
+        <v>104.32</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>10.056358</v>
+        <v>15.283459</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>94.099998</v>
+        <v>92.410004</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>9.724809</v>
+        <v>7.754199</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>109.449997</v>
+        <v>109.949997</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>3.128239</v>
+        <v>3.599359</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1305</v>
+        <v>1319</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>2.332876</v>
+        <v>3.4307</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7712.609863</v>
+        <v>7743.410156</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>0.344383</v>
+        <v>0.745108</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>180.869995</v>
+        <v>180.820007</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>3.484378</v>
+        <v>3.455778</v>
       </c>
     </row>
     <row r="63">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>451.149994</v>
+        <v>453</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>0.400576</v>
+        <v>0.812283</v>
       </c>
     </row>
     <row r="368">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>104.32</v>
+        <v>97.44000200000001</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>15.283459</v>
+        <v>7.680412</v>
       </c>
     </row>
     <row r="612">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>109.949997</v>
+        <v>110.449997</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>3.599359</v>
+        <v>4.070479</v>
       </c>
     </row>
     <row r="734">

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>180.820007</v>
+        <v>180.580002</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>3.455778</v>
+        <v>3.318459</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1866</v>
+        <v>5.2176</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-0.088603</v>
+        <v>0.508555</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51828.621094</v>
+        <v>51612.378906</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-2.55195</v>
+        <v>-2.958528</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9081</v>
+        <v>5.9337</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.689207</v>
+        <v>-1.263223</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>183477</v>
+        <v>183439.546875</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>3.414516</v>
+        <v>3.393406</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>453</v>
+        <v>453.25</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>0.812283</v>
+        <v>0.867919</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>528.25</v>
+        <v>522</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>2.572816</v>
+        <v>1.359223</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>27068.720703</v>
+        <v>26903.330078</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>2.646214</v>
+        <v>2.019042</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4321.200195</v>
+        <v>4170.799805</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-3.576923</v>
+        <v>-6.932951</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>97.44000200000001</v>
+        <v>97.69000200000001</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>7.680412</v>
+        <v>7.956686</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>92.410004</v>
+        <v>92.589996</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>7.754199</v>
+        <v>7.964079</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>110.449997</v>
+        <v>109.720001</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>4.070479</v>
+        <v>3.382648</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1319</v>
+        <v>1287</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>3.4307</v>
+        <v>0.921388</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7743.410156</v>
+        <v>7702.799805</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>0.745108</v>
+        <v>0.216749</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>180.580002</v>
+        <v>180.649994</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>3.318459</v>
+        <v>3.358505</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.2176</v>
+        <v>5.2163</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0.508555</v>
+        <v>0.483515</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51612.378906</v>
+        <v>51614.789062</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-2.958528</v>
+        <v>-2.953996</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9337</v>
+        <v>5.9327</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.263223</v>
+        <v>-1.279862</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>183439.546875</v>
+        <v>183466.265625</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>3.393406</v>
+        <v>3.408466</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>453.25</v>
+        <v>452.769989</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>0.867919</v>
+        <v>0.761096</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>1.359223</v>
+        <v>1.553398</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26903.330078</v>
+        <v>26899.5</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>2.019042</v>
+        <v>2.004518</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4170.799805</v>
+        <v>4170.399902</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-6.932951</v>
+        <v>-6.941874</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>97.69000200000001</v>
+        <v>97.769997</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>7.956686</v>
+        <v>8.045087000000001</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>92.589996</v>
+        <v>92.55999799999999</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>7.964079</v>
+        <v>7.929099</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>109.720001</v>
+        <v>109.889999</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>3.382648</v>
+        <v>3.542827</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1287</v>
+        <v>1288.25</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>0.921388</v>
+        <v>1.019408</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7702.799805</v>
+        <v>7702.350098</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>0.216749</v>
+        <v>0.210899</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>180.649994</v>
+        <v>179.699997</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>3.358505</v>
+        <v>2.814966</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.2163</v>
+        <v>5.2304</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0.483515</v>
+        <v>0.75513</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51614.789062</v>
+        <v>51159.171875</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-2.953996</v>
+        <v>-3.810646</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9327</v>
+        <v>5.9299</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.279862</v>
+        <v>-1.326454</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>183466.265625</v>
+        <v>182477.703125</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>3.408466</v>
+        <v>2.851275</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>452.769989</v>
+        <v>452.440002</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>0.761096</v>
+        <v>0.687659</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>523</v>
+        <v>521.25</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>1.553398</v>
+        <v>1.213592</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26899.5</v>
+        <v>26774.152344</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>2.004518</v>
+        <v>1.529193</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4170.399902</v>
+        <v>4183.600098</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-6.941874</v>
+        <v>-6.647326</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>97.769997</v>
+        <v>96.80999799999999</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>8.045087000000001</v>
+        <v>6.984197</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>92.55999799999999</v>
+        <v>90.720001</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>7.929099</v>
+        <v>5.783581</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>109.889999</v>
+        <v>108.629997</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>3.542827</v>
+        <v>2.355602</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1288.25</v>
+        <v>1297</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>1.019408</v>
+        <v>1.705548</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7702.350098</v>
+        <v>7660.640137</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>0.210899</v>
+        <v>-0.331766</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>179.699997</v>
+        <v>179.679993</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2.814966</v>
+        <v>2.803521</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.2304</v>
+        <v>5.2357</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0.75513</v>
+        <v>0.857227</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51159.171875</v>
+        <v>51162.320312</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-3.810646</v>
+        <v>-3.804727</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9299</v>
+        <v>5.9313</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.326454</v>
+        <v>-1.303158</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>182477.703125</v>
+        <v>182503.359375</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>2.851275</v>
+        <v>2.865736</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>452.440002</v>
+        <v>452.390015</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>0.687659</v>
+        <v>0.676535</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>521.25</v>
+        <v>522</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>1.213592</v>
+        <v>1.359223</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26774.152344</v>
+        <v>26779.210938</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>1.529193</v>
+        <v>1.548375</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4183.600098</v>
+        <v>4185.399902</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-6.647326</v>
+        <v>-6.607165</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>96.80999799999999</v>
+        <v>96.769997</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>6.984197</v>
+        <v>6.939992</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>90.720001</v>
+        <v>90.44000200000001</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>5.783581</v>
+        <v>5.45709</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>108.629997</v>
+        <v>108.690002</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>2.355602</v>
+        <v>2.412141</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1297</v>
+        <v>1298.75</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>1.705548</v>
+        <v>1.842776</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7660.640137</v>
+        <v>7660.899902</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-0.331766</v>
+        <v>-0.328386</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>179.679993</v>
+        <v>182.880005</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2.803521</v>
+        <v>4.634401</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.2357</v>
+        <v>5.1848</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0.857227</v>
+        <v>-0.123278</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51162.320312</v>
+        <v>51323.691406</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-3.804727</v>
+        <v>-3.501317</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9313</v>
+        <v>5.8759</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.303158</v>
+        <v>-2.22502</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>182503.359375</v>
+        <v>185742.0625</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>2.865736</v>
+        <v>4.69119</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>452.390015</v>
+        <v>450.890015</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>0.676535</v>
+        <v>0.342719</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>522</v>
+        <v>513.5</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>1.359223</v>
+        <v>-0.291262</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26779.210938</v>
+        <v>27077.017578</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>1.548375</v>
+        <v>2.677676</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4185.399902</v>
+        <v>4191.299805</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-6.607165</v>
+        <v>-6.475515</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>96.769997</v>
+        <v>98.83000199999999</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>6.939992</v>
+        <v>9.216493</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>90.44000200000001</v>
+        <v>91.379997</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>5.45709</v>
+        <v>6.553166</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>108.690002</v>
+        <v>110.900002</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>2.412141</v>
+        <v>4.494492</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1298.75</v>
+        <v>1309.75</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>1.842776</v>
+        <v>2.705352</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7660.899902</v>
+        <v>7715.97998</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-0.328386</v>
+        <v>0.388229</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>182.880005</v>
+        <v>183.020004</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>4.634401</v>
+        <v>4.714501</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1848</v>
+        <v>5.1838</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-0.123278</v>
+        <v>-0.14254</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51323.691406</v>
+        <v>51319.070312</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-3.501317</v>
+        <v>-3.510006</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8759</v>
+        <v>5.8751</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-2.22502</v>
+        <v>-2.238327</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>185742.0625</v>
+        <v>185892.640625</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>4.69119</v>
+        <v>4.776062</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>450.890015</v>
+        <v>451.519989</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>0.342719</v>
+        <v>0.482916</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>513.5</v>
+        <v>507.5</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-0.291262</v>
+        <v>-1.456311</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>27077.017578</v>
+        <v>27062.792969</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>2.677676</v>
+        <v>2.623735</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4191.299805</v>
+        <v>4189.299805</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-6.475515</v>
+        <v>-6.520143</v>
       </c>
     </row>
     <row r="551">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>110.900002</v>
+        <v>110.860001</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>4.494492</v>
+        <v>4.456802</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1309.75</v>
+        <v>1306.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>2.705352</v>
+        <v>2.4505</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7715.97998</v>
+        <v>7711.649902</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>0.388229</v>
+        <v>0.331893</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>181.050003</v>
+        <v>184.080002</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>3.587369</v>
+        <v>5.320977</v>
       </c>
     </row>
     <row r="62">
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>183.960007</v>
+        <v>184.139999</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.607293</v>
+        <v>0.032593</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.2282</v>
+        <v>5.225</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0.486268</v>
+        <v>0.424763</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>50836.351562</v>
+        <v>51103.199219</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-0.136917</v>
+        <v>0.387279</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8715</v>
+        <v>5.8793</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-0.419352</v>
+        <v>-0.287062</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>186810.84375</v>
+        <v>186864.640625</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>0.25268</v>
+        <v>0.28155</v>
       </c>
     </row>
     <row r="307">
@@ -24539,7 +24539,7 @@
         </is>
       </c>
       <c r="H366" t="n">
-        <v>451.529999</v>
+        <v>447.369995</v>
       </c>
       <c r="I366" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         </is>
       </c>
       <c r="N366" t="n">
-        <v>0.485144</v>
+        <v>-0.440639</v>
       </c>
     </row>
     <row r="367">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>451.859985</v>
+        <v>454.899994</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>0.07308199999999999</v>
+        <v>1.68317</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>497.75</v>
+        <v>496.25</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-0.599101</v>
+        <v>-0.898652</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26818.607422</v>
+        <v>27210.888672</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-0.158047</v>
+        <v>1.302362</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4195.399902</v>
+        <v>4160.399902</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>0.207794</v>
+        <v>-0.6281870000000001</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>101.080002</v>
+        <v>101.379997</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>-2.366461</v>
+        <v>-2.076694</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>91.910004</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>1.647872</v>
+        <v>0.442382</v>
       </c>
     </row>
     <row r="673">
@@ -48683,7 +48683,7 @@
         </is>
       </c>
       <c r="H732" t="n">
-        <v>109.650002</v>
+        <v>111.93</v>
       </c>
       <c r="I732" t="inlineStr">
         <is>
@@ -48711,7 +48711,7 @@
         </is>
       </c>
       <c r="N732" t="n">
-        <v>3.316691</v>
+        <v>5.464999</v>
       </c>
     </row>
     <row r="733">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>112.709999</v>
+        <v>113.480003</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>2.790695</v>
+        <v>1.384797</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1277.25</v>
+        <v>1279</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>-1.218097</v>
+        <v>-1.082753</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7647.740234</v>
+        <v>7723.790039</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-0.049661</v>
+        <v>0.944254</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>184.139999</v>
+        <v>184.320007</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0.032593</v>
+        <v>0.130381</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.225</v>
+        <v>5.2234</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0.424763</v>
+        <v>0.394015</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51103.199219</v>
+        <v>51112.210938</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>0.387279</v>
+        <v>0.404982</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8793</v>
+        <v>5.8805</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-0.287062</v>
+        <v>-0.266714</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>186864.640625</v>
+        <v>187130.234375</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>0.28155</v>
+        <v>0.424082</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>454.899994</v>
+        <v>454.670013</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>1.68317</v>
+        <v>1.631763</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>496.25</v>
+        <v>496.75</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-0.898652</v>
+        <v>-0.798802</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>27210.888672</v>
+        <v>27222.126953</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>1.302362</v>
+        <v>1.3442</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4160.399902</v>
+        <v>4155.200195</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-0.6281870000000001</v>
+        <v>-0.752383</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>101.379997</v>
+        <v>101.400002</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>-2.076694</v>
+        <v>-2.057372</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>90.81999999999999</v>
+        <v>90.970001</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>0.442382</v>
+        <v>0.608276</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>113.480003</v>
+        <v>113.379997</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>1.384797</v>
+        <v>1.29545</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1279</v>
+        <v>1279.25</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>-1.082753</v>
+        <v>-1.063418</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7723.790039</v>
+        <v>7725.560059</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>0.944254</v>
+        <v>0.967387</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>184.320007</v>
+        <v>184.410004</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0.130381</v>
+        <v>0.179271</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.2234</v>
+        <v>5.2223</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0.394015</v>
+        <v>0.372871</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51112.210938</v>
+        <v>51176.960938</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>0.404982</v>
+        <v>0.532177</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8805</v>
+        <v>5.8702</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-0.266714</v>
+        <v>-0.441397</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>187130.234375</v>
+        <v>192115</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>0.424082</v>
+        <v>3.099174</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>454.670013</v>
+        <v>452.079987</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>1.631763</v>
+        <v>1.052818</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>496.75</v>
+        <v>497.75</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-0.798802</v>
+        <v>-0.599101</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>27222.126953</v>
+        <v>27190.859375</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>1.3442</v>
+        <v>1.227795</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4155.200195</v>
+        <v>4162.299805</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-0.752383</v>
+        <v>-0.582807</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>101.400002</v>
+        <v>102.25</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>-2.057372</v>
+        <v>-1.236355</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>90.970001</v>
+        <v>91.110001</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>0.608276</v>
+        <v>0.763108</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>113.379997</v>
+        <v>113.019997</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>1.29545</v>
+        <v>0.97382</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1279.25</v>
+        <v>1278.25</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>-1.063418</v>
+        <v>-1.140758</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7725.560059</v>
+        <v>7722.720215</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>0.967387</v>
+        <v>0.930273</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>184.410004</v>
+        <v>190</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0.179271</v>
+        <v>3.215992</v>
       </c>
     </row>
     <row r="63">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>452.079987</v>
+        <v>454.700012</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>1.052818</v>
+        <v>1.638469</v>
       </c>
     </row>
     <row r="368">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>113.019997</v>
+        <v>116.339996</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>0.97382</v>
+        <v>3.939959</v>
       </c>
     </row>
     <row r="734">

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>190</v>
+        <v>205.960007</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>3.215992</v>
+        <v>11.886139</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.2223</v>
+        <v>4.9902</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0.372871</v>
+        <v>-4.088103</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51176.960938</v>
+        <v>51352.410156</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>0.532177</v>
+        <v>0.87683</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8702</v>
+        <v>5.6059</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-0.441397</v>
+        <v>-4.923931</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>192115</v>
+        <v>208982.96875</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>3.099174</v>
+        <v>12.151427</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>454.700012</v>
+        <v>439.059998</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>1.638469</v>
+        <v>-1.857522</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>497.75</v>
+        <v>497.5</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-0.599101</v>
+        <v>-0.649026</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>27190.859375</v>
+        <v>27504.978516</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>1.227795</v>
+        <v>2.397217</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4162.299805</v>
+        <v>4167</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-0.582807</v>
+        <v>-0.470542</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>102.25</v>
+        <v>100</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>-1.236355</v>
+        <v>-3.409639</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>91.110001</v>
+        <v>88.980003</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>0.763108</v>
+        <v>-1.592562</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>116.339996</v>
+        <v>128.25</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>3.939959</v>
+        <v>14.580541</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1278.25</v>
+        <v>1281</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>-1.140758</v>
+        <v>-0.928074</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7722.720215</v>
+        <v>7785.040039</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>0.930273</v>
+        <v>1.744747</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>205.960007</v>
+        <v>202.289993</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>11.886139</v>
+        <v>9.892433</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>4.9902</v>
+        <v>4.9748</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-4.088103</v>
+        <v>-4.38409</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51352.410156</v>
+        <v>51601.289062</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>0.87683</v>
+        <v>1.365728</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.6059</v>
+        <v>5.601</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-4.923931</v>
+        <v>-5.007035</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>208982.96875</v>
+        <v>205427.203125</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>12.151427</v>
+        <v>10.243213</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>439.059998</v>
+        <v>440.369995</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.857522</v>
+        <v>-1.5647</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>497.5</v>
+        <v>506.5</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-0.649026</v>
+        <v>1.148278</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>27504.978516</v>
+        <v>27662.966797</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>2.397217</v>
+        <v>2.985386</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4167</v>
+        <v>4191.299805</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-0.470542</v>
+        <v>0.109862</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>100</v>
+        <v>99.75</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>-3.409639</v>
+        <v>-3.651114</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>88.980003</v>
+        <v>89.220001</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>-1.592562</v>
+        <v>-1.327137</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>128.25</v>
+        <v>128.529999</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>14.580541</v>
+        <v>14.830696</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1281</v>
+        <v>1295.75</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>-0.928074</v>
+        <v>0.212684</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7785.040039</v>
+        <v>7834.240234</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>1.744747</v>
+        <v>2.387757</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>202.289993</v>
+        <v>201.839996</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>9.892433</v>
+        <v>9.647976</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>4.9748</v>
+        <v>4.9916</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-4.38409</v>
+        <v>-4.061195</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51601.289062</v>
+        <v>51213.96875</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>1.365728</v>
+        <v>0.6048750000000001</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.601</v>
+        <v>5.5874</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-5.007035</v>
+        <v>-5.237689</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>205427.203125</v>
+        <v>204957.3125</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>10.243213</v>
+        <v>9.991045</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>440.369995</v>
+        <v>439.339996</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.5647</v>
+        <v>-1.794935</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>506.5</v>
+        <v>501.25</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>1.148278</v>
+        <v>0.09984999999999999</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>27662.966797</v>
+        <v>27498.011719</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>2.985386</v>
+        <v>2.371281</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4191.299805</v>
+        <v>4135.399902</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>0.109862</v>
+        <v>-1.225316</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>99.75</v>
+        <v>100.699997</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>-3.651114</v>
+        <v>-2.733509</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>89.220001</v>
+        <v>88.779999</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>-1.327137</v>
+        <v>-1.813757</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>128.529999</v>
+        <v>130.240005</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>14.830696</v>
+        <v>16.358443</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1295.75</v>
+        <v>1293.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>0.212684</v>
+        <v>0.03867</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7834.240234</v>
+        <v>7800.709961</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>2.387757</v>
+        <v>1.949541</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>201.839996</v>
+        <v>202.75</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>9.647976</v>
+        <v>10.142328</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>4.9916</v>
+        <v>5.0122</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-4.061195</v>
+        <v>-3.665265</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51213.96875</v>
+        <v>51085.648438</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>0.6048750000000001</v>
+        <v>0.352802</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.5874</v>
+        <v>5.6139</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-5.237689</v>
+        <v>-4.788245</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>204957.3125</v>
+        <v>205987.65625</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>9.991045</v>
+        <v>10.543982</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>439.339996</v>
+        <v>438.910004</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.794935</v>
+        <v>-1.89105</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>501.25</v>
+        <v>500</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>0.09984999999999999</v>
+        <v>-0.149775</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>27498.011719</v>
+        <v>27173.046875</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>2.371281</v>
+        <v>1.161482</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4135.399902</v>
+        <v>4147.5</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-1.225316</v>
+        <v>-0.936303</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>100.699997</v>
+        <v>103.629997</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>-2.733509</v>
+        <v>0.09658899999999999</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>88.779999</v>
+        <v>91.05999799999999</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>-1.813757</v>
+        <v>0.707807</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>130.240005</v>
+        <v>133.270004</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>16.358443</v>
+        <v>19.065491</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1293.5</v>
+        <v>1288</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>0.03867</v>
+        <v>-0.386698</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7800.709961</v>
+        <v>7747.589844</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>1.949541</v>
+        <v>1.2553</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>202.75</v>
+        <v>203.580002</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>10.142328</v>
+        <v>10.59322</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.0122</v>
+        <v>5.0001</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-3.665265</v>
+        <v>-3.897822</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51085.648438</v>
+        <v>51122.460938</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>0.352802</v>
+        <v>0.425117</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.6139</v>
+        <v>5.6081</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-4.788245</v>
+        <v>-4.886617</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>205987.65625</v>
+        <v>206768.96875</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>10.543982</v>
+        <v>10.963276</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>438.910004</v>
+        <v>438.649994</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.89105</v>
+        <v>-1.94917</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>500</v>
+        <v>500.5</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-0.149775</v>
+        <v>-0.049925</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>27173.046875</v>
+        <v>27225.183594</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>1.161482</v>
+        <v>1.35558</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4147.5</v>
+        <v>4157.899902</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-0.936303</v>
+        <v>-0.6879</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>103.629997</v>
+        <v>103.290001</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>0.09658899999999999</v>
+        <v>-0.231815</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>91.05999799999999</v>
+        <v>90.800003</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>0.707807</v>
+        <v>0.420266</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>133.270004</v>
+        <v>133.729996</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>19.065491</v>
+        <v>19.476454</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1288</v>
+        <v>1287.75</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>-0.386698</v>
+        <v>-0.406032</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7747.589844</v>
+        <v>7758.700195</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>1.2553</v>
+        <v>1.400504</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>203.580002</v>
+        <v>205.360001</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>10.59322</v>
+        <v>11.56019</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.0001</v>
+        <v>4.9842</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-3.897822</v>
+        <v>-4.203424</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51122.460938</v>
+        <v>51618.488281</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>0.425117</v>
+        <v>1.399514</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.6081</v>
+        <v>5.577</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-4.886617</v>
+        <v>-5.41407</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>206768.96875</v>
+        <v>208674.40625</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>10.963276</v>
+        <v>11.985836</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>438.649994</v>
+        <v>439.200012</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.94917</v>
+        <v>-1.826225</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>500.5</v>
+        <v>472.5</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-0.049925</v>
+        <v>-5.641538</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>27225.183594</v>
+        <v>27350.091797</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>1.35558</v>
+        <v>1.820595</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4157.899902</v>
+        <v>4210.899902</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-0.6879</v>
+        <v>0.578014</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>103.290001</v>
+        <v>104.099998</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>-0.231815</v>
+        <v>0.550565</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>90.800003</v>
+        <v>91.480003</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>0.420266</v>
+        <v>1.172313</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>133.729996</v>
+        <v>138.789993</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>19.476454</v>
+        <v>23.997135</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1287.75</v>
+        <v>1274.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>-0.406032</v>
+        <v>-1.430781</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7758.700195</v>
+        <v>7807.779785</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>1.400504</v>
+        <v>2.041939</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>205.360001</v>
+        <v>205.149994</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>11.56019</v>
+        <v>11.446106</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>4.9842</v>
+        <v>4.9872</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-4.203424</v>
+        <v>-4.145768</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51618.488281</v>
+        <v>51627.800781</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>1.399514</v>
+        <v>1.417808</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.577</v>
+        <v>5.5779</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-5.41407</v>
+        <v>-5.398809</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>208674.40625</v>
+        <v>208473.4375</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>11.985836</v>
+        <v>11.877985</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>439.200012</v>
+        <v>439.23999</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.826225</v>
+        <v>-1.817289</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>472.5</v>
+        <v>470.25</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-5.641538</v>
+        <v>-6.090864</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>27350.091797</v>
+        <v>27376.107422</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>1.820595</v>
+        <v>1.917448</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4210.899902</v>
+        <v>4214.100098</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>0.578014</v>
+        <v>0.654451</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>104.099998</v>
+        <v>103.879997</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>0.550565</v>
+        <v>0.338065</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>91.480003</v>
+        <v>91.199997</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>1.172313</v>
+        <v>0.86264</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>138.789993</v>
+        <v>138.770004</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>23.997135</v>
+        <v>23.979276</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1274.5</v>
+        <v>1273</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>-1.430781</v>
+        <v>-1.54679</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7807.779785</v>
+        <v>7812.879883</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>2.041939</v>
+        <v>2.108593</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>205.149994</v>
+        <v>203.080002</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>11.446106</v>
+        <v>10.321599</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>4.9872</v>
+        <v>4.9772</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-4.145768</v>
+        <v>-4.337964</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51627.800781</v>
+        <v>51654.949219</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>1.417808</v>
+        <v>1.471138</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.5779</v>
+        <v>5.5828</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-5.398809</v>
+        <v>-5.315706</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>208473.4375</v>
+        <v>209067</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>11.877985</v>
+        <v>12.196522</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>439.23999</v>
+        <v>440.350006</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.817289</v>
+        <v>-1.569168</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>470.25</v>
+        <v>479.75</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-6.090864</v>
+        <v>-4.193709</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>27376.107422</v>
+        <v>27366.169922</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>1.917448</v>
+        <v>1.880452</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4214.100098</v>
+        <v>4216.299805</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>0.654451</v>
+        <v>0.706991</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>103.879997</v>
+        <v>104.720001</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>0.338065</v>
+        <v>1.149428</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>91.199997</v>
+        <v>91.849998</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>0.86264</v>
+        <v>1.581509</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>138.770004</v>
+        <v>134.389999</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>23.979276</v>
+        <v>20.066112</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1273</v>
+        <v>1292</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>-1.54679</v>
+        <v>-0.07734000000000001</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7812.879883</v>
+        <v>7811.540039</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>2.108593</v>
+        <v>2.091082</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>203.080002</v>
+        <v>205.550003</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>10.321599</v>
+        <v>11.663408</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>4.9772</v>
+        <v>4.9918</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-4.337964</v>
+        <v>-4.057355</v>
       </c>
     </row>
     <row r="124">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>440.350006</v>
+        <v>439.25</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.569168</v>
+        <v>-1.815051</v>
       </c>
     </row>
     <row r="368">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>134.389999</v>
+        <v>139.800003</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>20.066112</v>
+        <v>24.899493</v>
       </c>
     </row>
     <row r="734">

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>4.9918</v>
+        <v>4.9863</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-4.057355</v>
+        <v>-4.163062</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51654.949219</v>
+        <v>51815.429688</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>1.471138</v>
+        <v>1.786387</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.5828</v>
+        <v>5.5628</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-5.315706</v>
+        <v>-5.654905</v>
       </c>
     </row>
     <row r="246">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>479.75</v>
+        <v>483.5</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-4.193709</v>
+        <v>-3.444833</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>27366.169922</v>
+        <v>27238.013672</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>1.880452</v>
+        <v>1.403344</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4216.299805</v>
+        <v>4188.399902</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>0.706991</v>
+        <v>0.040598</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>104.720001</v>
+        <v>106.470001</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>1.149428</v>
+        <v>2.839759</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>91.849998</v>
+        <v>93.55999799999999</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>1.581509</v>
+        <v>3.472682</v>
       </c>
     </row>
     <row r="673">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1292</v>
+        <v>1288.25</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>-0.07734000000000001</v>
+        <v>-0.367363</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7811.540039</v>
+        <v>7801.430176</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>2.091082</v>
+        <v>1.958954</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51815.429688</v>
+        <v>51821.851562</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>1.786387</v>
+        <v>1.799002</v>
       </c>
     </row>
     <row r="185">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>27238.013672</v>
+        <v>27254.84375</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>1.403344</v>
+        <v>1.466</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4188.399902</v>
+        <v>4192</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>0.040598</v>
+        <v>0.126587</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>106.470001</v>
+        <v>106.489998</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>2.839759</v>
+        <v>2.859074</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>93.55999799999999</v>
+        <v>93.540001</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>3.472682</v>
+        <v>3.450567</v>
       </c>
     </row>
     <row r="673">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7801.430176</v>
+        <v>7805.220215</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>1.958954</v>
+        <v>2.008487</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>205.550003</v>
+        <v>203.5</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>11.663408</v>
+        <v>10.54976</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>4.9863</v>
+        <v>5.0137</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-4.163062</v>
+        <v>-3.636432</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51821.851562</v>
+        <v>51644.039062</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>1.799002</v>
+        <v>1.449706</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.5628</v>
+        <v>5.6095</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-5.654905</v>
+        <v>-4.862873</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>209067</v>
+        <v>206741.546875</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>12.196522</v>
+        <v>10.94856</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>439.25</v>
+        <v>441.290009</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.815051</v>
+        <v>-1.359051</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>483.5</v>
+        <v>482.5</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-3.444833</v>
+        <v>-3.644533</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>27254.84375</v>
+        <v>27187.478516</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>1.466</v>
+        <v>1.215209</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4192</v>
+        <v>4177.399902</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>0.126587</v>
+        <v>-0.222139</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>106.489998</v>
+        <v>105.959999</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>2.859074</v>
+        <v>2.347146</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>93.540001</v>
+        <v>94.290001</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>3.450567</v>
+        <v>4.28003</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>139.800003</v>
+        <v>135.210007</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>24.899493</v>
+        <v>20.798719</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1288.25</v>
+        <v>1284</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>-0.367363</v>
+        <v>-0.696056</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7805.220215</v>
+        <v>7797.970215</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>2.008487</v>
+        <v>1.913735</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>203.5</v>
+        <v>201.429993</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>10.54976</v>
+        <v>9.425245</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.0137</v>
+        <v>5.0395</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-3.636432</v>
+        <v>-3.14055</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51644.039062</v>
+        <v>51627.679688</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>1.449706</v>
+        <v>1.41757</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.6095</v>
+        <v>5.6045</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-4.862873</v>
+        <v>-4.947675</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>206741.546875</v>
+        <v>204498.546875</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>10.94856</v>
+        <v>9.744846000000001</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>441.290009</v>
+        <v>441.929993</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.359051</v>
+        <v>-1.215996</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>482.5</v>
+        <v>480</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-3.644533</v>
+        <v>-4.143784</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>27187.478516</v>
+        <v>26954.634766</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>1.215209</v>
+        <v>0.348364</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4177.399902</v>
+        <v>4118.200195</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-0.222139</v>
+        <v>-1.636133</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>105.959999</v>
+        <v>105.910004</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>2.347146</v>
+        <v>2.298855</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>94.290001</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>4.28003</v>
+        <v>5.419157</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>135.210007</v>
+        <v>131.199997</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>20.798719</v>
+        <v>17.216114</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1284</v>
+        <v>1278</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>-0.696056</v>
+        <v>-1.160093</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7797.970215</v>
+        <v>7748.819824</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>1.913735</v>
+        <v>1.271375</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>201.429993</v>
+        <v>201.509995</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>9.425245</v>
+        <v>9.468705</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.0395</v>
+        <v>5.0385</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-3.14055</v>
+        <v>-3.159778</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51627.679688</v>
+        <v>51619.429688</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>1.41757</v>
+        <v>1.401364</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.6045</v>
+        <v>5.607</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-4.947675</v>
+        <v>-4.905274</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>204498.546875</v>
+        <v>204599.5</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>9.744846000000001</v>
+        <v>9.799023</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>441.929993</v>
+        <v>441.399994</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.215996</v>
+        <v>-1.334466</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>480</v>
+        <v>479.75</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-4.143784</v>
+        <v>-4.193709</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26954.634766</v>
+        <v>26941.662109</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>0.348364</v>
+        <v>0.300068</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4118.200195</v>
+        <v>4125.299805</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-1.636133</v>
+        <v>-1.466558</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>105.910004</v>
+        <v>105.650002</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>2.298855</v>
+        <v>2.047718</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>95.31999999999999</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>5.419157</v>
+        <v>4.987837</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>131.199997</v>
+        <v>130.940002</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>17.216114</v>
+        <v>16.983831</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1278</v>
+        <v>1278.25</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>-1.160093</v>
+        <v>-1.140758</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7748.819824</v>
+        <v>7748.359863</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>1.271375</v>
+        <v>1.265364</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>201.509995</v>
+        <v>202.300003</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>9.468705</v>
+        <v>9.897871</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.0385</v>
+        <v>5.0463</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-3.159778</v>
+        <v>-3.00986</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51619.429688</v>
+        <v>51953.851562</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>1.401364</v>
+        <v>2.058303</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.607</v>
+        <v>5.6621</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-4.905274</v>
+        <v>-3.970779</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>204599.5</v>
+        <v>205512.375</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>9.799023</v>
+        <v>10.288921</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>441.399994</v>
+        <v>438.640015</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.334466</v>
+        <v>-1.951401</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>479.75</v>
+        <v>480.25</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-4.193709</v>
+        <v>-4.093859</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26941.662109</v>
+        <v>26452.943359</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>0.300068</v>
+        <v>-1.519364</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4125.299805</v>
+        <v>4180.600098</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-1.466558</v>
+        <v>-0.145702</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>105.650002</v>
+        <v>105.209999</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>2.047718</v>
+        <v>1.622718</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>94.93000000000001</v>
+        <v>95.040001</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>4.987837</v>
+        <v>5.109492</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>130.940002</v>
+        <v>132.309998</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>16.983831</v>
+        <v>18.207806</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1278.25</v>
+        <v>1274.75</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>-1.140758</v>
+        <v>-1.411446</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7748.359863</v>
+        <v>7697.810059</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>1.265364</v>
+        <v>0.604715</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>202.300003</v>
+        <v>202.639999</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>9.897871</v>
+        <v>10.082571</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.0463</v>
+        <v>5.0767</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-3.00986</v>
+        <v>-2.425565</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51953.851562</v>
+        <v>52400.160156</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>2.058303</v>
+        <v>2.935033</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.6621</v>
+        <v>5.7122</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-3.970779</v>
+        <v>-3.121077</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>205512.375</v>
+        <v>205726.09375</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>10.288921</v>
+        <v>10.403614</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>438.640015</v>
+        <v>443.209991</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.951401</v>
+        <v>-0.92988</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>480.25</v>
+        <v>473.75</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-4.093859</v>
+        <v>-5.391912</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26452.943359</v>
+        <v>26499.583984</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-1.519364</v>
+        <v>-1.345727</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4180.600098</v>
+        <v>4207.799805</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-0.145702</v>
+        <v>0.503968</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>105.209999</v>
+        <v>105.459999</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>1.622718</v>
+        <v>1.864194</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>95.040001</v>
+        <v>95.589996</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>5.109492</v>
+        <v>5.71776</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>132.309998</v>
+        <v>131.389999</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>18.207806</v>
+        <v>17.385865</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1274.75</v>
+        <v>1253.75</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>-1.411446</v>
+        <v>-3.035576</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7697.810059</v>
+        <v>7733.080078</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>0.604715</v>
+        <v>1.065668</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>202.639999</v>
+        <v>201.389999</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>10.082571</v>
+        <v>9.403518999999999</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.0767</v>
+        <v>5.0693</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-2.425565</v>
+        <v>-2.567794</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52400.160156</v>
+        <v>52002.410156</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>2.935033</v>
+        <v>2.153692</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.7122</v>
+        <v>5.7053</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-3.121077</v>
+        <v>-3.238106</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>205726.09375</v>
+        <v>205430</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>10.403614</v>
+        <v>10.244714</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>443.209991</v>
+        <v>444.450012</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-0.92988</v>
+        <v>-0.6526999999999999</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>473.75</v>
+        <v>474.25</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-5.391912</v>
+        <v>-5.292062</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26499.583984</v>
+        <v>26140.029297</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-1.345727</v>
+        <v>-2.684299</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4207.799805</v>
+        <v>4181.100098</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>0.503968</v>
+        <v>-0.133759</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>105.459999</v>
+        <v>109.860001</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>1.864194</v>
+        <v>6.114172</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>95.589996</v>
+        <v>101.410004</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>5.71776</v>
+        <v>12.154397</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>131.389999</v>
+        <v>130.830002</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>17.385865</v>
+        <v>16.885555</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1253.75</v>
+        <v>1261.25</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>-3.035576</v>
+        <v>-2.45553</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7733.080078</v>
+        <v>7659.439941</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>1.065668</v>
+        <v>0.103246</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>201.429993</v>
+        <v>204.220001</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>9.425245</v>
+        <v>10.940895</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.0579</v>
+        <v>5.01</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-2.786907</v>
+        <v>-3.707542</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52020.359375</v>
+        <v>52561.949219</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>2.188951</v>
+        <v>3.252852</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.673</v>
+        <v>5.6383</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-3.785914</v>
+        <v>-4.374425</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>204667.15625</v>
+        <v>207377.765625</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>9.835331</v>
+        <v>11.289989</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>440.230011</v>
+        <v>437.529999</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.595991</v>
+        <v>-2.199521</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>467.75</v>
+        <v>462.75</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-6.590115</v>
+        <v>-7.588617</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26522.501953</v>
+        <v>26544.773438</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-1.260407</v>
+        <v>-1.177493</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4161.899902</v>
+        <v>4169.299805</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-0.592359</v>
+        <v>-0.415611</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>109.400002</v>
+        <v>107</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>5.669857</v>
+        <v>3.351687</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>98.599998</v>
+        <v>96.30999799999999</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>9.046671999999999</v>
+        <v>6.514045</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>133.410004</v>
+        <v>137.440002</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>19.190568</v>
+        <v>22.791032</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1251</v>
+        <v>1253.25</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>-3.24826</v>
+        <v>-3.074246</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7708.77002</v>
+        <v>7736.75</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>0.747954</v>
+        <v>1.113632</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>204.220001</v>
+        <v>204.389999</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>10.940895</v>
+        <v>11.033245</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.01</v>
+        <v>5.023</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-3.707542</v>
+        <v>-3.45769</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52561.949219</v>
+        <v>52536.589844</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>3.252852</v>
+        <v>3.203036</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.6383</v>
+        <v>5.6414</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-4.374425</v>
+        <v>-4.32185</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>207377.765625</v>
+        <v>207602.875</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>11.289989</v>
+        <v>11.410795</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>437.529999</v>
+        <v>438.600006</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-2.199521</v>
+        <v>-1.960344</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>462.75</v>
+        <v>456.25</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-7.588617</v>
+        <v>-8.886670000000001</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26544.773438</v>
+        <v>26607.212891</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-1.177493</v>
+        <v>-0.94504</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4169.299805</v>
+        <v>4149.100098</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-0.415611</v>
+        <v>-0.898084</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>107</v>
+        <v>109.040001</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>3.351687</v>
+        <v>5.322131</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>96.30999799999999</v>
+        <v>97.800003</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>6.514045</v>
+        <v>8.161917000000001</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>137.440002</v>
+        <v>137.669998</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>22.791032</v>
+        <v>22.996514</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1253.25</v>
+        <v>1238.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>-3.074246</v>
+        <v>-4.215004</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7736.75</v>
+        <v>7733.419922</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>1.113632</v>
+        <v>1.07011</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>204.389999</v>
+        <v>200.619995</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>11.033245</v>
+        <v>8.98522</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.023</v>
+        <v>5.0487</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-3.45769</v>
+        <v>-2.963733</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52536.589844</v>
+        <v>52570.058594</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>3.203036</v>
+        <v>3.268782</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.6414</v>
+        <v>5.6493</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-4.32185</v>
+        <v>-4.187862</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>207602.875</v>
+        <v>203775.984375</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>11.410795</v>
+        <v>9.357081000000001</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>438.600006</v>
+        <v>435.700012</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.960344</v>
+        <v>-2.608575</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>456.25</v>
+        <v>459.75</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-8.886670000000001</v>
+        <v>-8.187718</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26607.212891</v>
+        <v>26096.677734</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-0.94504</v>
+        <v>-2.845691</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4149.100098</v>
+        <v>4069.300049</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-0.898084</v>
+        <v>-2.804121</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>109.040001</v>
+        <v>111.389999</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>5.322131</v>
+        <v>7.592003</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>97.800003</v>
+        <v>98.410004</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>8.161917000000001</v>
+        <v>8.836546999999999</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>137.669998</v>
+        <v>134.389999</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>22.996514</v>
+        <v>20.066112</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1238.5</v>
+        <v>1263.75</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>-4.215004</v>
+        <v>-2.262181</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7733.419922</v>
+        <v>7649.620117</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>1.07011</v>
+        <v>-0.025092</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>200.619995</v>
+        <v>200.830002</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>8.98522</v>
+        <v>9.099304999999999</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.0487</v>
+        <v>5.044</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-2.963733</v>
+        <v>-3.054062</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52570.058594</v>
+        <v>52102.460938</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>3.268782</v>
+        <v>2.350232</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.6493</v>
+        <v>5.6461</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-4.187862</v>
+        <v>-4.242135</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>203775.984375</v>
+        <v>203917.265625</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>9.357081000000001</v>
+        <v>9.4329</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>435.700012</v>
+        <v>433.559998</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-2.608575</v>
+        <v>-3.08693</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>459.75</v>
+        <v>457.75</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-8.187718</v>
+        <v>-8.587119</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26096.677734</v>
+        <v>25972.888672</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-2.845691</v>
+        <v>-3.306541</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4069.300049</v>
+        <v>4010.300049</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-2.804121</v>
+        <v>-4.213346</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>111.389999</v>
+        <v>111.139999</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>7.592003</v>
+        <v>7.350527</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>98.410004</v>
+        <v>102.190002</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>8.836546999999999</v>
+        <v>13.017037</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>134.389999</v>
+        <v>134.300003</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>20.066112</v>
+        <v>19.985708</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1263.75</v>
+        <v>1271.75</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>-2.262181</v>
+        <v>-1.643465</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7649.620117</v>
+        <v>7620.830078</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-0.025092</v>
+        <v>-0.401357</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>200.830002</v>
+        <v>201.690002</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>9.099304999999999</v>
+        <v>9.566492999999999</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.044</v>
+        <v>4.9964</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-3.054062</v>
+        <v>-3.968941</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52102.460938</v>
+        <v>52215.160156</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>2.350232</v>
+        <v>2.571618</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.6461</v>
+        <v>5.5626</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-4.242135</v>
+        <v>-5.658294</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>203917.265625</v>
+        <v>205083</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>9.4329</v>
+        <v>10.058495</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>433.559998</v>
+        <v>430</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-3.08693</v>
+        <v>-3.882691</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>457.75</v>
+        <v>456</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-8.587119</v>
+        <v>-8.936595000000001</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>25972.888672</v>
+        <v>25955.339844</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-3.306541</v>
+        <v>-3.371872</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4010.300049</v>
+        <v>4007.899902</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-4.213346</v>
+        <v>-4.270673</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>111.139999</v>
+        <v>116.720001</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>7.350527</v>
+        <v>12.740271</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>102.190002</v>
+        <v>103.269997</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>13.017037</v>
+        <v>14.211456</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>134.300003</v>
+        <v>137.160004</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>19.985708</v>
+        <v>22.540877</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1271.75</v>
+        <v>1256.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>-1.643465</v>
+        <v>-2.822892</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7620.830078</v>
+        <v>7623.680176</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-0.401357</v>
+        <v>-0.364108</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>4.9964</v>
+        <v>4.9652</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-3.968941</v>
+        <v>-4.568606</v>
       </c>
     </row>
     <row r="124">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>116.720001</v>
+        <v>111.699997</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>12.740271</v>
+        <v>7.891431</v>
       </c>
     </row>
     <row r="612">

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>201.690002</v>
+        <v>170.990005</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>9.566492999999999</v>
+        <v>-7.111037</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>4.9652</v>
+        <v>5.4467</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-4.568606</v>
+        <v>4.685851</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52215.160156</v>
+        <v>52373.011719</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>2.571618</v>
+        <v>2.881702</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.5626</v>
+        <v>6.0905</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-5.658294</v>
+        <v>3.294886</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>205083</v>
+        <v>173958.859375</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>10.058495</v>
+        <v>-6.644382</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>430</v>
+        <v>471.690002</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-3.882691</v>
+        <v>5.436218</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-8.936595000000001</v>
+        <v>-9.335996</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>25955.339844</v>
+        <v>26216.0625</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-3.371872</v>
+        <v>-2.401238</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4007.899902</v>
+        <v>4032.800049</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-4.270673</v>
+        <v>-3.675929</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>111.699997</v>
+        <v>111.949997</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>7.891431</v>
+        <v>8.132906999999999</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>103.269997</v>
+        <v>102.870003</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>14.211456</v>
+        <v>13.769083</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>137.160004</v>
+        <v>100.959999</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>22.540877</v>
+        <v>-9.800769000000001</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1256.5</v>
+        <v>1248.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>-2.822892</v>
+        <v>-3.441609</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7623.680176</v>
+        <v>7681.919922</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-0.364108</v>
+        <v>0.397043</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>170.990005</v>
+        <v>173.179993</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>-7.111037</v>
+        <v>-5.921343</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.4467</v>
+        <v>5.3271</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>4.685851</v>
+        <v>2.387128</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52373.011719</v>
+        <v>52447.628906</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>2.881702</v>
+        <v>3.028281</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>6.0905</v>
+        <v>5.9472</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>3.294886</v>
+        <v>0.864517</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>173958.859375</v>
+        <v>176027.578125</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>-6.644382</v>
+        <v>-5.534197</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>471.690002</v>
+        <v>465.970001</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>5.436218</v>
+        <v>4.157634</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>454</v>
+        <v>451.5</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-9.335996</v>
+        <v>-9.835247000000001</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26216.0625</v>
+        <v>26448.109375</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-2.401238</v>
+        <v>-1.53736</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4032.800049</v>
+        <v>4072.300049</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-3.675929</v>
+        <v>-2.732466</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>111.949997</v>
+        <v>109.370003</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>8.132906999999999</v>
+        <v>5.640881</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>102.870003</v>
+        <v>100.040001</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>13.769083</v>
+        <v>10.639242</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>100.959999</v>
+        <v>100.730003</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-9.800769000000001</v>
+        <v>-10.006251</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1248.5</v>
+        <v>1249.75</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>-3.441609</v>
+        <v>-3.344934</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7681.919922</v>
+        <v>7721.919922</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>0.397043</v>
+        <v>0.919813</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>173.179993</v>
+        <v>168.339996</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>-5.921343</v>
+        <v>-8.550632999999999</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.3271</v>
+        <v>5.3707</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>2.387128</v>
+        <v>3.225124</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52447.628906</v>
+        <v>52486.179688</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>3.028281</v>
+        <v>3.10401</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9472</v>
+        <v>5.9943</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>0.864517</v>
+        <v>1.663334</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>176027.578125</v>
+        <v>171106.125</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>-5.534197</v>
+        <v>-8.175311000000001</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>465.970001</v>
+        <v>469.320007</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>4.157634</v>
+        <v>4.906456</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>451.5</v>
+        <v>451.75</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-9.835247000000001</v>
+        <v>-9.785322000000001</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26448.109375</v>
+        <v>26453.009766</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-1.53736</v>
+        <v>-1.519116</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4072.300049</v>
+        <v>4051.699951</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-2.732466</v>
+        <v>-3.224502</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>109.370003</v>
+        <v>112.5</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>5.640881</v>
+        <v>8.664156999999999</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>100.040001</v>
+        <v>103.459999</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>10.639242</v>
+        <v>14.421589</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>100.730003</v>
+        <v>94.989998</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-10.006251</v>
+        <v>-15.134461</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1249.75</v>
+        <v>1243</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>-3.344934</v>
+        <v>-3.866976</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7721.919922</v>
+        <v>7734.149902</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>0.919813</v>
+        <v>1.07965</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>165.490005</v>
+        <v>165.399994</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>-10.098868</v>
+        <v>-10.147766</v>
       </c>
     </row>
     <row r="62">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>5.4297</v>
+        <v>5.3848</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>4.359107</v>
+        <v>3.496128</v>
       </c>
     </row>
     <row r="122">
@@ -12335,7 +12335,7 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>51957.371094</v>
+        <v>51770.308594</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>2.065217</v>
+        <v>1.697751</v>
       </c>
     </row>
     <row r="182">
@@ -16293,7 +16293,7 @@
         </is>
       </c>
       <c r="H241" t="n">
-        <v>6.0641</v>
+        <v>6.0193</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>2.847141</v>
+        <v>2.087336</v>
       </c>
     </row>
     <row r="242">
@@ -20251,7 +20251,7 @@
         </is>
       </c>
       <c r="H301" t="n">
-        <v>168219.609375</v>
+        <v>167922</v>
       </c>
       <c r="I301" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         </is>
       </c>
       <c r="N301" t="n">
-        <v>-9.72437</v>
+        <v>-9.884083</v>
       </c>
     </row>
     <row r="302">
@@ -24209,7 +24209,7 @@
         </is>
       </c>
       <c r="H361" t="n">
-        <v>465.75</v>
+        <v>466.5</v>
       </c>
       <c r="I361" t="inlineStr">
         <is>
@@ -24237,7 +24237,7 @@
         </is>
       </c>
       <c r="N361" t="n">
-        <v>4.108457</v>
+        <v>4.276104</v>
       </c>
     </row>
     <row r="362">
@@ -32125,7 +32125,7 @@
         </is>
       </c>
       <c r="H481" t="n">
-        <v>25479.597656</v>
+        <v>25437</v>
       </c>
       <c r="I481" t="inlineStr">
         <is>
@@ -32153,7 +32153,7 @@
         </is>
       </c>
       <c r="N481" t="n">
-        <v>-5.142995</v>
+        <v>-5.30158</v>
       </c>
     </row>
     <row r="482">
@@ -36083,7 +36083,7 @@
         </is>
       </c>
       <c r="H541" t="n">
-        <v>3906</v>
+        <v>3898.899902</v>
       </c>
       <c r="I541" t="inlineStr">
         <is>
@@ -36111,7 +36111,7 @@
         </is>
       </c>
       <c r="N541" t="n">
-        <v>-6.704569</v>
+        <v>-6.874156</v>
       </c>
     </row>
     <row r="542">
@@ -40041,7 +40041,7 @@
         </is>
       </c>
       <c r="H601" t="n">
-        <v>113.879997</v>
+        <v>117.639999</v>
       </c>
       <c r="I601" t="inlineStr">
         <is>
@@ -40069,7 +40069,7 @@
         </is>
       </c>
       <c r="N601" t="n">
-        <v>9.997101000000001</v>
+        <v>13.628901</v>
       </c>
     </row>
     <row r="602">
@@ -43999,7 +43999,7 @@
         </is>
       </c>
       <c r="H661" t="n">
-        <v>104.360001</v>
+        <v>104.120003</v>
       </c>
       <c r="I661" t="inlineStr">
         <is>
@@ -44027,7 +44027,7 @@
         </is>
       </c>
       <c r="N661" t="n">
-        <v>15.416946</v>
+        <v>15.151521</v>
       </c>
     </row>
     <row r="662">
@@ -47957,7 +47957,7 @@
         </is>
       </c>
       <c r="H721" t="n">
-        <v>91.81999999999999</v>
+        <v>92.150002</v>
       </c>
       <c r="I721" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         </is>
       </c>
       <c r="N721" t="n">
-        <v>-17.966587</v>
+        <v>-17.671758</v>
       </c>
     </row>
     <row r="722">
@@ -51915,7 +51915,7 @@
         </is>
       </c>
       <c r="H781" t="n">
-        <v>1235.25</v>
+        <v>1222.25</v>
       </c>
       <c r="I781" t="inlineStr">
         <is>
@@ -51943,7 +51943,7 @@
         </is>
       </c>
       <c r="N781" t="n">
-        <v>-4.466357</v>
+        <v>-5.471771</v>
       </c>
     </row>
     <row r="782">
@@ -55873,7 +55873,7 @@
         </is>
       </c>
       <c r="H841" t="n">
-        <v>7594.609863</v>
+        <v>7580.069824</v>
       </c>
       <c r="I841" t="inlineStr">
         <is>
@@ -55901,7 +55901,7 @@
         </is>
       </c>
       <c r="N841" t="n">
-        <v>-0.744036</v>
+        <v>-0.934063</v>
       </c>
     </row>
   </sheetData>
